--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-02-24T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-03-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-02-24T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-03-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-02-23T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-11-30T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-02-23T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-03-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-02-22T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-03-01T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-02-23T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-02-21T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-02-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-02-23T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-01T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-02-23T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-03-02T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-02-23T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-03-02T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-02-22T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-02-23T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-02-24T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-03-03T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-02-23T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-03-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-12-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-02-24T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-03-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-02-23T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-03-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-10-28T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-11-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2025-10-07T23:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2025-11-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-10-28T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-11-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-02-23T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-03-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-02-23T23:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-03-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-02-23T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2025-12-31T23:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-01-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>['1999-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
+          <t>['1999-01-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2023-09-29T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2023-09-29T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2023-09-29T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2023-09-29T00:00:00.000Z', '2026-02-20T23:00:00.000Z']</t>
+          <t>['2023-09-29T00:00:00.000Z', '2026-02-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2023-09-29T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-02-14T16:34:55.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-02-21T17:17:11.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-02-15T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-02-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-02-14T12:25:54.234Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-02-21T13:08:05.229Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-02-15T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2023-04-18T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2023-04-18T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-07T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-06T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-06T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-06T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-06T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-06T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-02-06T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-02T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-02-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-02-06T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-02T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-02-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-02-14T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-02-14T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-02-13T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-02-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-02-14T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-02-14T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-13T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-02-14T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-02-14T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-02-13T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-02-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-01-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>['1981-10-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1981-10-01T00:00:00.000Z', '2024-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2024-11-04T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-01-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-15T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-01-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-15T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-01-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-15T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-01-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-15T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-01-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-02-09T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-02-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-02-14T00:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-02-21T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-02-13T21:15:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-02-21T10:25:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-02-14T21:53:10.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-02-21T21:45:06.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-02-13T23:51:45.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-02-20T23:13:12.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10682,7 +10682,7 @@
         <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-02-14T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-02-13T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-02-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-14T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-14T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-14T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-14T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-14T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-02-14T21:52:03.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-02-21T22:34:18.000Z']</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2023-06-08T00:00:00.000Z', '2026-02-26T21:00:00.000Z']</t>
+          <t>['2023-06-08T00:00:00.000Z', '2026-02-28T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-02-14T07:15:56.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-02-21T06:56:15.000Z']</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-02-14T22:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-02-21T22:10:00.000Z']</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-02-14T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-02-21T22:28:00.000Z']</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-14T23:14:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-21T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-14T22:14:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-21T22:15:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-14T22:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-21T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-02-13T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-02-20T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-08T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-02-04T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-02-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-13T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-08T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -16070,7 +16070,7 @@
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>['Baltic Sea', 'Black Sea']</t>
+          <t>['Black Sea']</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -21826,7 +21826,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>['Mediterranean Sea']</t>
+          <t>['Baltic Sea']</t>
         </is>
       </c>
       <c r="G287" t="inlineStr"/>

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-03-03T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-03-03T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-03-02T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-03-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-03-01T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-03-08T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-02-28T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-03-07T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-01T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-08T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-03-02T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-03-09T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-03-02T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-03-09T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-03-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>['1980-01-01T01:00:00.000Z', '2025-11-01T00:00:00.000Z']</t>
+          <t>['1980-01-01T01:00:00.000Z', '2025-12-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-03-03T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-03-10T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-03-02T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-03-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-03-03T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-03-02T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-03-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-03-02T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-03-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-03-02T23:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-03-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2023-09-29T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2024-01-25T01:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2023-09-29T00:00:00.000Z', '2026-02-27T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-03-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-12-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2025-09-30T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2025-10-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-11-30T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-02-21T17:17:11.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-02-28T16:20:59.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-02-22T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-02-21T13:08:05.229Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-02-28T13:01:34.322Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2023-04-18T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2023-04-18T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7482,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-09T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-02-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-02-13T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-09T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-02-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-02-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-02-20T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-02-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-20T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-02-20T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-02-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-22T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-01-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-22T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-01-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-22T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-01-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-22T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-01-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-02-16T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-02-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-02-21T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-02-28T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-02-21T10:25:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-02-28T08:35:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-02-21T21:45:06.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-02-28T22:08:52.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Arctic Ocean - High Resolution Sea Ice Information L3</t>
+          <t>Baltic Sea - Sea Ice Concentration and Thickness Charts</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_ARC_PHY_AUTO_L3_MYNRT_011_023.jpg</t>
+          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_BAL_SEAICE_L4_NRT_OBSERVATIONS_011_004.jpg</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -10639,23 +10639,23 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>['Arctic Ocean']</t>
+          <t>['Baltic Sea']</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>{'row': {'magnitude': 0.5, 'units': 'km'}, 'column': {'magnitude': 0.5, 'units': 'km'}}</t>
+          <t>{'row': {'magnitude': 1, 'units': 'km'}, 'column': {'magnitude': 1, 'units': 'km'}}</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
+          <t>2019-05-04</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>[-179.994, 31.001999999999995, 179.994, 89.994]</t>
+          <t>[9, 53.20000076293945, 31, 66.19999694824219]</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-02-20T23:13:12.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10682,11 +10682,11 @@
         <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>{'basemapId': 'dark', 'overlays': {'tags': [{'name': 'High resolution'}]}}</t>
+          <t>{'basemapId': 'dark', 'overlays': {'tags': []}}</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr"/>
@@ -10700,12 +10700,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Baltic Sea - Sea Ice Concentration and Thickness Charts</t>
+          <t>Baltic Sea - SAR Sea Ice Thickness and Drift, Multisensor Sea Ice Concentration</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_BAL_SEAICE_L4_NRT_OBSERVATIONS_011_004.jpg</t>
+          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_BAL_SEAICE_L4_NRT_OBSERVATIONS_011_011.jpg</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -10725,28 +10725,28 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>{'row': {'magnitude': 1, 'units': 'km'}, 'column': {'magnitude': 1, 'units': 'km'}}</t>
+          <t>{'row': {'magnitude': 0.8, 'units': 'km'}, 'column': {'magnitude': 0.8, 'units': 'km'}}</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2019-05-04</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>['Daily']</t>
+          <t>['Irregular', 'Daily']</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>[9, 53.20000076293945, 31, 66.19999694824219]</t>
+          <t>[9, 53, 31, 66]</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2020-03-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10758,7 +10758,7 @@
         <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
@@ -10776,12 +10776,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Baltic Sea - SAR Sea Ice Thickness and Drift, Multisensor Sea Ice Concentration</t>
+          <t>Global Ocean Sea Ice Concentration Time Series REPROCESSED (OSI-SAF)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_BAL_SEAICE_L4_NRT_OBSERVATIONS_011_011.jpg</t>
+          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_GLO_SEAICE_L4_REP_OBSERVATIONS_011_009.jpg</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -10796,33 +10796,33 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>['Baltic Sea']</t>
+          <t>['Global Ocean', 'Arctic Ocean', 'Antarctic Ocean']</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>{'row': {'magnitude': 0.8, 'units': 'km'}, 'column': {'magnitude': 0.8, 'units': 'km'}}</t>
+          <t>{'row': {'magnitude': 25, 'units': 'km'}, 'column': {'magnitude': 25, 'units': 'km'}}</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>1979-01-01</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>['Irregular', 'Daily']</t>
+          <t>['Daily']</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>[9, 53, 31, 66]</t>
+          <t>[-180, -90, 179.79999999997955, 90]</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>['2020-03-01T00:00:00.000Z', None]</t>
+          <t>['1978-10-25T12:00:00.000Z', '2025-09-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -10834,14 +10834,18 @@
         <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>{'basemapId': 'dark', 'overlays': {'tags': []}}</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr"/>
+          <t>{'basemapId': 'light', 'overlays': {'tags': []}}</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
       <c r="R136" t="inlineStr"/>
     </row>
     <row r="137">
@@ -10852,12 +10856,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Global Ocean Sea Ice Concentration Time Series REPROCESSED (OSI-SAF)</t>
+          <t>Arctic Ocean - Sea Ice Thickness REPROCESSED</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_GLO_SEAICE_L4_REP_OBSERVATIONS_011_009.jpg</t>
+          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_GLO_PHY_CLIMATE_L3_MY_011_013.jpg</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -10867,12 +10871,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>['Global Ocean', 'Arctic Ocean', 'Antarctic Ocean']</t>
+          <t>['Global Ocean', 'Arctic Ocean']</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10883,22 +10887,22 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1979-01-01</t>
+          <t>1995-10-01</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>['Daily']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>[-180, -90, 179.79999999997955, 90]</t>
+          <t>[-180, 0, 179.79999999997955, 90]</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2025-09-29T00:00:00.000Z']</t>
+          <t>['1995-10-01T00:00:00.000Z', '2024-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -10910,16 +10914,16 @@
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>{'basemapId': 'light', 'overlays': {'tags': []}}</t>
+          <t>{'basemapId': 'light', 'overlays': {'tags': [{'name': 'C3S'}]}}</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="R137" t="inlineStr"/>
@@ -10932,12 +10936,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Arctic Ocean - Sea Ice Thickness REPROCESSED</t>
+          <t>Global Ocean - High Resolution SAR Sea Ice Drift Time Series</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_GLO_PHY_CLIMATE_L3_MY_011_013.jpg</t>
+          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_GLO_PHY_L4_MY_011_020.jpg</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -10947,38 +10951,38 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>['Global Ocean', 'Arctic Ocean']</t>
+          <t>['Global Ocean']</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>{'row': {'magnitude': 25, 'units': 'km'}, 'column': {'magnitude': 25, 'units': 'km'}}</t>
+          <t>{'row': {'magnitude': 10, 'units': 'km'}, 'column': {'magnitude': 10, 'units': 'km'}}</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1995-10-01</t>
+          <t>2014-10-05</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Daily']</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>[-180, 0, 179.79999999997955, 90]</t>
+          <t>[-179.95, -89.95, 179.95000000000005, 89.95]</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>['1995-10-01T00:00:00.000Z', '2024-04-01T00:00:00.000Z']</t>
+          <t>['2014-10-06T00:00:00.000Z', '2025-11-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -10990,18 +10994,14 @@
         <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>{'basemapId': 'light', 'overlays': {'tags': [{'name': 'C3S'}]}}</t>
-        </is>
-      </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>2024-04-30</t>
-        </is>
-      </c>
+          <t>{'basemapId': 'light', 'overlays': {'tags': [{'name': 'Ice drift'}]}}</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
     </row>
     <row r="139">
@@ -11012,12 +11012,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Global Ocean - High Resolution SAR Sea Ice Drift Time Series</t>
+          <t>Antarctic Ocean Sea Ice Drift REPROCESSED</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_GLO_PHY_L4_MY_011_020.jpg</t>
+          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_ANT_PHY_L3_MY_011_018.jpg</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -11027,23 +11027,23 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>['Global Ocean']</t>
+          <t>['Antarctic Ocean']</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>{'row': {'magnitude': 10, 'units': 'km'}, 'column': {'magnitude': 10, 'units': 'km'}}</t>
+          <t>{'row': {'magnitude': 62.5, 'units': 'km'}, 'column': {'magnitude': 62.5, 'units': 'km'}}</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2014-10-05</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>[-179.95, -89.95, 179.95000000000005, 89.95]</t>
+          <t>[-179.75, -90, 180, -40.25]</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>['2014-10-06T00:00:00.000Z', '2025-11-01T00:00:00.000Z']</t>
+          <t>['2003-04-01T00:00:00.000Z', '2025-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -11070,7 +11070,7 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
@@ -11088,12 +11088,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Antarctic Ocean Sea Ice Drift REPROCESSED</t>
+          <t>Arctic Ocean - Sea and Ice Surface Temperature L3S REPROCESSED</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_ANT_PHY_L3_MY_011_018.jpg</t>
+          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_ARC_PHY_CLIMATE_L3_MY_011_021.jpg</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -11108,18 +11108,18 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>['Antarctic Ocean']</t>
+          <t>['Arctic Ocean']</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>{'row': {'magnitude': 62.5, 'units': 'km'}, 'column': {'magnitude': 62.5, 'units': 'km'}}</t>
+          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -11129,28 +11129,28 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>[-179.75, -90, 180, -40.25]</t>
+          <t>[-179.97500610351562, 58, 179.97500610351562, 89.94999694824219]</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>['2003-04-01T00:00:00.000Z', '2025-06-30T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>['Sea ice']</t>
+          <t>['Temperature', 'Sea ice']</t>
         </is>
       </c>
       <c r="N140" t="b">
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>{'basemapId': 'light', 'overlays': {'tags': [{'name': 'Ice drift'}]}}</t>
+          <t>{'basemapId': 'light', 'overlays': {'tags': [{'name': 'SST'}, {'name': 'Ice surface temperature'}]}}</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr"/>
@@ -11164,12 +11164,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Arctic Ocean - Sea and Ice Surface Temperature L3S REPROCESSED</t>
+          <t>Arctic Ocean - Sea and Ice Surface Temperature L4 REPROCESSED</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_ARC_PHY_CLIMATE_L3_MY_011_021.jpg</t>
+          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_ARC_PHY_CLIMATE_L4_MY_011_016.jpg</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -11222,14 +11222,18 @@
         <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>{'basemapId': 'light', 'overlays': {'tags': [{'name': 'SST'}, {'name': 'Ice surface temperature'}]}}</t>
         </is>
       </c>
-      <c r="Q141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
       <c r="R141" t="inlineStr"/>
     </row>
     <row r="142">
@@ -11240,12 +11244,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Arctic Ocean - Sea and Ice Surface Temperature L4 REPROCESSED</t>
+          <t>Arctic Ocean - High Resolution Sea Ice Information L3</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_ARC_PHY_CLIMATE_L4_MY_011_016.jpg</t>
+          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/SEAICE_ARC_PHY_AUTO_L3_MYNRT_011_023.jpg</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -11255,7 +11259,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -11265,13 +11269,13 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
+          <t>{'row': {'magnitude': 0.5, 'units': 'km'}, 'column': {'magnitude': 0.5, 'units': 'km'}}</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -11281,35 +11285,31 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>[-179.97500610351562, 58, 179.97500610351562, 89.94999694824219]</t>
+          <t>[-179.994, 31.001999999999995, 179.994, 89.994]</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-02-27T23:43:47.000Z']</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>['Temperature', 'Sea ice']</t>
+          <t>['Sea ice']</t>
         </is>
       </c>
       <c r="N142" t="b">
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>{'basemapId': 'light', 'overlays': {'tags': [{'name': 'SST'}, {'name': 'Ice surface temperature'}]}}</t>
-        </is>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>2023-12-31</t>
-        </is>
-      </c>
+          <t>{'basemapId': 'light', 'overlays': {'tags': [{'name': 'High resolution'}]}}</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
     </row>
     <row r="143">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-02-20T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-02-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-02-21T22:34:18.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-02-28T21:24:45.000Z']</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-02-21T06:56:15.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-02-28T07:44:03.000Z']</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-02-21T22:10:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-02-28T22:10:00.000Z']</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-02-21T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-02-28T22:28:00.000Z']</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-02-14T18:42:59.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-02-28T20:43:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-21T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-28T22:15:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-21T22:15:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-28T22:15:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-21T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-28T22:10:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-02-20T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-02-27T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-15T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-02-11T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-02-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-20T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-15T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-03-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-03-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-12-23T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-01-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2025-11-30T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2025-12-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-03-09T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-03-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-03-08T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-03-15T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-03-07T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-03-14T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-08T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-15T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-03-09T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-03-09T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-03-08T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-03-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-03-10T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-03-17T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-03-09T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-03-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-03-09T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-03-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-03-09T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-03-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-03-09T23:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-03-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-01-25T01:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2024-01-25T01:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-03-06T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-03-13T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-02-28T16:20:59.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-03-07T17:03:45.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-03-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-02-28T13:01:34.322Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-03-07T15:49:47.000Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-03-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://catalogue.marine.copernicus.eu/documents/IMG/OCEANCOLOUR_ARC_BGC_HR_L3_NRT_009_201.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OCEANCOLOUR_ARC_BGC_HR_L3_NRT_009_201.png</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://catalogue.marine.copernicus.eu/documents/IMG/OCEANCOLOUR_ARC_BGC_HR_L4_NRT_009_207.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OCEANCOLOUR_ARC_BGC_HR_L4_NRT_009_207.png</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>['2020-01-08T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['2020-01-08T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2023-04-18T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2023-04-18T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>['2024-08-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['2024-08-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>['2020-01-02T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['2020-01-02T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>['2020-01-04T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['2020-01-04T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-21T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-16T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-02-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-02-20T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-16T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-02-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-02-26T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-02-27T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-03-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-27T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-02-27T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-03-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-29T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-29T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-29T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-29T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-02-23T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-02-28T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-03-07T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-02-28T08:35:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-03-07T08:25:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-02-28T22:08:52.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-03-07T21:29:38.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-02-27T23:43:47.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-03-06T23:27:30.000Z']</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-02-27T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-03-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-02-28T21:24:45.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-03-07T21:52:32.000Z']</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2023-06-08T00:00:00.000Z', '2026-02-28T21:00:00.000Z']</t>
+          <t>['2023-06-08T00:00:00.000Z', '2026-03-19T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-02-28T07:44:03.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-03-07T06:39:22.000Z']</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2046-01-01T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-07T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -13520,7 +13520,7 @@
         <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>838</v>
+        <v>808</v>
       </c>
       <c r="P171" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-02-28T22:10:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-03-07T22:10:00.000Z']</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-02-28T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-03-07T20:28:00.000Z']</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-02-28T20:43:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-03-07T20:43:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-28T22:15:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-07T23:10:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14393,12 +14393,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>[-165.84800720214844, -49.099998474121094, 179.1741943359375, 78.4000015258789]</t>
+          <t>[-165.84800720214844, -64.9000015258789, 179.1741943359375, 78.4000015258789]</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-28T22:15:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-07T22:13:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-28T22:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-07T23:10:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-02-27T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-03-06T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-22T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-02-18T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-02-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-27T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-22T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-03-17T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-03-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-03-17T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-03-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-03-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-01-20T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2025-12-31T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-01-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-01-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-03-16T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-03-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-03-15T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-03-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-03-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-03-14T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-03-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-15T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-23T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-03-23T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-03-23T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-03-12T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-03-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-03-17T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-03-24T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-03-16T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-03-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>['1950-01-08T00:00:00.000Z', '2025-12-31T23:00:00.000Z']</t>
+          <t>['1950-01-08T00:00:00.000Z', '2026-02-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>['1992-01-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['1992-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-03-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-03-16T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-03-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-11-18T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-12-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-11-18T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-12-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-03-16T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-03-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-03-16T23:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-03-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-03-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>['1987-01-01T00:00:00.000Z', '2026-01-31T23:00:00.000Z']</t>
+          <t>['1987-01-01T00:00:00.000Z', '2026-02-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-01-25T01:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2024-01-25T01:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-03-13T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-03-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-03-07T17:03:45.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-03-14T17:47:43.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-03-08T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-03-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-03-07T15:49:47.000Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-03-14T16:26:21.000Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-03-08T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-03-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2023-04-18T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2023-04-18T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-05T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-23T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-02-27T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-23T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-03-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-03-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-03-06T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-03-13T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-06T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-13T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-03-06T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-03-13T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-02-05T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-02-05T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-02-05T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-02-05T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-03-07T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-03-14T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-03-07T08:25:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-03-14T10:20:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-03-07T21:29:38.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-03-14T21:18:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-03-06T23:27:30.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-03-13T23:51:53.000Z']</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-03-06T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-03-13T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['1991-08-01T00:00:00.000Z', '2025-10-31T00:00:00.000Z']</t>
+          <t>['1991-08-01T00:00:00.000Z', '2025-11-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['1994-06-01T00:00:00.000Z', '2025-10-21T23:00:00.000Z']</t>
+          <t>['1994-06-01T00:00:00.000Z', '2025-11-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>['1994-07-01T00:00:00.000Z', '2025-10-01T00:00:00.000Z']</t>
+          <t>['1994-07-01T00:00:00.000Z', '2025-11-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-03-07T21:52:32.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-03-14T22:26:40.000Z']</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2023-06-08T00:00:00.000Z', '2026-03-19T21:00:00.000Z']</t>
+          <t>['2024-03-26T00:00:00.000Z', '2026-03-25T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>['2023-01-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['2023-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-03-07T06:39:22.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-03-14T06:50:37.000Z']</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-07T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-14T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -13658,7 +13658,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2025-03-31T23:52:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2025-03-31T23:55:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13670,7 +13670,7 @@
         <v>0</v>
       </c>
       <c r="O173" t="n">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="P173" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-03-07T22:10:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-03-14T22:20:00.000Z']</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-03-07T20:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-03-14T22:28:00.000Z']</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-03-07T20:43:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-03-10T18:34:59.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-07T23:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-14T22:13:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-07T22:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-14T22:13:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-07T23:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-14T23:10:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-03-06T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-03-13T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-02-25T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-03-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-06T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-13T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-03-24T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-03-24T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-03-23T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-03-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-03-23T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-03-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-03-21T23:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-03-28T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-03-23T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-03-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-03-21T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-03-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-23T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-29T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>['1991-01-01T00:00:00.000Z', '2025-10-31T00:00:00.000Z']</t>
+          <t>['1991-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-03-23T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-03-30T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-03-23T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-03-30T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-03-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>['1980-01-01T01:00:00.000Z', '2025-12-01T00:00:00.000Z']</t>
+          <t>['1980-01-01T01:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-03-23T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-03-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-03-24T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-03-31T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-03-23T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-03-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-03-24T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-03-23T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-03-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-03-23T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-03-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-03-23T23:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-03-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-03-23T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-03-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-01-31T23:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-02-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>['1999-01-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['1999-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-01-25T01:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-03-20T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-03-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-03-14T17:47:43.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-03-21T16:51:35.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-03-15T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-03-14T16:26:21.000Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-03-21T13:11:56.246Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-03-15T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>['2020-01-08T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['2020-01-08T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2023-04-18T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2023-04-18T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>['2020-01-02T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['2020-01-02T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>['2020-01-04T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['2020-01-04T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-03-07T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-03-06T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-02T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-03-12T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-03-12T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-12T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-03-13T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-03-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-13T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-03-13T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-03-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>['1981-10-01T00:00:00.000Z', '2024-07-31T00:00:00.000Z']</t>
+          <t>['1981-10-01T00:00:00.000Z', '2025-12-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2025-11-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-02-12T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-02-12T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-02-12T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-02-12T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-03-14T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-03-21T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-03-14T10:20:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-03-20T20:30:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-03-14T21:18:00.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-03-21T21:45:11.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-03-13T23:51:53.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-03-20T23:19:47.000Z']</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-03-13T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-03-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-03-14T22:26:40.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-03-21T22:11:12.000Z']</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2024-03-26T00:00:00.000Z', '2026-03-25T21:00:00.000Z']</t>
+          <t>['2024-03-26T00:00:00.000Z', '2026-03-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-03-14T06:50:37.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-03-21T06:11:15.000Z']</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-14T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-21T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -13520,7 +13520,7 @@
         <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="P171" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-03-14T22:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-03-21T22:20:00.000Z']</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-03-14T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-03-21T22:28:00.000Z']</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-14T22:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-21T22:15:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-14T22:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-21T22:14:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-14T23:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-21T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-03-13T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-03-20T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-08T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-03-04T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-03-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-13T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-08T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-04-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-04-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-03-30T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-04-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-03-30T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-04-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-03-28T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-03-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-03-30T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-04-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-03-28T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-04-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-29T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-04-05T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-03-30T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-04-06T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-03-30T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-04-06T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-03-29T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-04-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-03-30T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-04-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-03-31T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-04-07T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-03-30T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-04-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-04-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-03-30T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-04-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-03-30T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-04-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-03-30T23:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-04-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-03-30T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-04-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-03-27T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-04-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2025-10-31T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2025-11-30T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-01-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-03-21T16:51:35.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-03-28T17:34:15.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-03-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-03-21T13:11:56.246Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-03-28T15:13:38.260Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-03-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2023-04-18T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2023-04-18T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-03-14T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-03-13T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-09T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-03-20T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-03-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-20T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-03-20T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-03-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-02-19T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-02-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-03-16T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-03-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-03-21T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-03-28T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-03-20T20:30:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-03-28T08:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-03-21T21:45:11.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-03-28T22:40:47.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-03-20T23:19:47.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-03-27T23:35:50.000Z']</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['1991-12-03T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1991-12-03T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-03-20T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-03-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-03-21T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-03-21T22:11:12.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-03-28T22:14:02.000Z']</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-03-21T06:11:15.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-03-28T05:29:03.000Z']</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-21T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-28T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-03-21T22:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-03-28T22:20:00.000Z']</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-03-21T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-03-28T22:28:00.000Z']</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>[-180, -78.57160186767578, 179.99986267089844, 89.55000305175781]</t>
+          <t>[-180, -78.63800048828125, 179.99986267089844, 89.55000305175781]</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-21T22:15:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-28T22:19:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-21T22:14:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-28T22:19:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-21T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-28T22:10:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-03-20T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-03-27T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-15T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-03-11T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-03-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-20T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-03-20T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-15T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R308"/>
+  <dimension ref="A1:R307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-04-14T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-04-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-04-14T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-04-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-04-13T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-04-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-04-13T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-04-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-04-07T11:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-04-12T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-04-13T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-04-11T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-04-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-12T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-04-19T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-04-13T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-04-20T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-04-13T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-04-20T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-04-12T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-04-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-04-13T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-04-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-04-14T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-04-21T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-04-13T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-04-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>['1950-01-08T00:00:00.000Z', '2026-02-28T23:00:00.000Z']</t>
+          <t>['1950-01-08T00:00:00.000Z', '2026-03-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-04-14T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-04-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-04-13T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-04-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-12-02T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-12-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-12-02T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-12-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-04-13T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-04-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-04-14T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-04-21T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-04-13T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-04-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-04-10T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-04-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-04-04T16:38:21.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-04-11T17:20:49.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-04-05T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-04-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-04-04T15:23:15.000Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-04-11T14:50:30.039Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-04-05T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-04-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5023,12 +5023,12 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1992-10-03</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>['Daily']</t>
+          <t>['Instantaneous']</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>['1992-10-13T00:32:22.000Z', '2025-08-02T23:50:18.000Z']</t>
+          <t>['1992-10-13T00:32:22.000Z', '2025-10-18T23:50:14.000Z']</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5057,11 +5057,7 @@
           <t>{'basemapId': 'light', 'overlays': {'tags': []}}</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>2020-12-31</t>
-        </is>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -5118,7 +5114,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-08-02T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-10-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5194,7 +5190,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>['1992-10-13T05:51:26.000Z', '2025-08-02T23:28:34.000Z']</t>
+          <t>['1992-10-13T05:51:26.000Z', '2025-10-18T23:42:44.000Z']</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5270,7 +5266,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-08-02T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-10-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5342,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5418,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5798,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5874,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5950,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6026,7 +6022,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>['2020-01-08T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2020-01-08T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6102,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2023-04-18T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2023-04-18T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6254,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6330,7 +6326,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>['2020-01-02T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2020-01-02T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6406,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6482,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6558,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6634,7 +6630,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6710,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6786,7 +6782,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6862,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6938,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7014,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7090,7 +7086,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>['2020-01-04T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['2020-01-04T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7318,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7394,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7470,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7622,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7698,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7774,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7850,7 +7846,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7926,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8002,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-28T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8078,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-03-27T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8154,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-23T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8230,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8306,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8382,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8458,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8534,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8610,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8686,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8762,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-04-03T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-04-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8838,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8914,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8990,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-03T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9066,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9142,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9218,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-04-03T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-04-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9834,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-03-05T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9910,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-03-05T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9986,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-03-05T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10062,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-03-05T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10138,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10214,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-03-30T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-04-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10290,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-04-04T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-04-11T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10366,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10442,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10518,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10594,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-04-04T10:25:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-04-10T20:55:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10670,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-04-04T22:00:10.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-04-11T21:22:02.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10746,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10883,7 +10879,7 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1979-01-01</t>
+          <t>1978-10-25</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -10917,11 +10913,7 @@
           <t>{'basemapId': 'light', 'overlays': {'tags': []}}</t>
         </is>
       </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
+      <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
     </row>
     <row r="138">
@@ -11442,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-04-03T23:31:59.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-04-10T23:29:19.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11518,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11750,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11822,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-04-03T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-04-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11898,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11974,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12050,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12126,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12202,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12906,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-04-04T22:37:05.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-04-11T22:08:08.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12982,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13130,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2024-03-26T00:00:00.000Z', '2026-03-31T21:00:00.000Z']</t>
+          <t>['2024-03-26T00:00:00.000Z', '2026-04-21T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13516,7 +13508,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>['2024-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['2024-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -13588,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-04-04T09:30:56.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-04-11T05:23:26.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13660,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-04T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-11T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14262,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-04-04T23:40:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-04-11T23:40:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14334,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-04-04T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-04-11T22:28:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14406,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-03-30T00:01:30.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-03-30T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14478,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-04T22:14:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-11T23:11:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14550,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-04T21:12:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-11T21:13:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14622,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-04T23:58:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-11T23:40:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14698,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-04-03T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-04-10T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14774,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-29T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14852,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-03-25T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -15002,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-03T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15156,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15308,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-29T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15384,7 +15376,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -15414,17 +15406,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Surface ocean carbon fields</t>
+          <t>Global coastal satellite derived bathymetry static</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/MULTIOBS_GLO_BIO_CARBON_SURFACE_MYNRT_015_008.jpg</t>
+          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/BATHYMETRY_GLO_PHY_COASTAL_L4_MY_016_001.jpg</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>['In-situ observations']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -15439,44 +15431,36 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>{'row': {'magnitude': 0.25, 'units': 'degree'}, 'column': {'magnitude': 0.25, 'units': 'degree'}}</t>
+          <t>{'row': {'magnitude': 100, 'units': 'm'}, 'column': {'magnitude': 100, 'units': 'm'}}</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>1985-01-15</t>
-        </is>
-      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>[-179.875, -89.875, 179.875, 89.875]</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
-        </is>
-      </c>
+          <t>[-179.99947916666667, -89.99947916666666, 179.99947916779914, 89.99947916654406]</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>['Carbonate system']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="N197" t="b">
         <v>0</v>
       </c>
       <c r="O197" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>{'basemapId': 'light', 'overlays': {'tags': [{'name': 'Surface carbon'}]}}</t>
+          <t>{'basemapId': 'light', 'overlays': {'tags': []}}</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr"/>
@@ -15490,65 +15474,69 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Global coastal satellite derived bathymetry static</t>
+          <t>Antarctic Sea Ice Extent from Reanalysis</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/BATHYMETRY_GLO_PHY_COASTAL_L4_MY_016_001.jpg</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent.png</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
+          <t>['Numerical models']</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>['Global Ocean']</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 100, 'units': 'm'}, 'column': {'magnitude': 100, 'units': 'm'}}</t>
-        </is>
-      </c>
+          <t>['Global Ocean', 'Antarctic Ocean']</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>1993-01-01</t>
+        </is>
+      </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>[-179.99947916666667, -89.99947916666666, 179.99947916779914, 89.99947916654406]</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr"/>
+          <t>[-180, -90, 180, 0]</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Sea ice']</t>
         </is>
       </c>
       <c r="N198" t="b">
         <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>12</v>
-      </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>{'basemapId': 'light', 'overlays': {'tags': []}}</t>
-        </is>
-      </c>
-      <c r="Q198" t="inlineStr"/>
-      <c r="R198" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent-hq.png</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -15558,17 +15546,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Antarctic Sea Ice Extent from Reanalysis</t>
+          <t>Antarctic Monthly Sea Ice Extent from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent_obs.png</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -15581,7 +15569,7 @@
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1979-01-01</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -15596,7 +15584,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1979-01-01T00:00:00.000Z', '2025-05-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -15608,17 +15596,17 @@
         <v>0</v>
       </c>
       <c r="O199" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -15630,30 +15618,30 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Antarctic Monthly Sea Ice Extent from Observations Reprocessing</t>
+          <t>Arctic Sea Ice Extent from Reanalysis</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent.png</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>['Global Ocean', 'Antarctic Ocean']</t>
+          <t>['Arctic Ocean']</t>
         </is>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>1979-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -15663,12 +15651,12 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>[-180, -90, 180, 0]</t>
+          <t>[-180, 0, 180, 90]</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>['1979-01-01T00:00:00.000Z', '2025-05-05T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -15680,17 +15668,17 @@
         <v>0</v>
       </c>
       <c r="O200" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent-hq.png</t>
         </is>
       </c>
     </row>
@@ -15702,17 +15690,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Arctic Sea Ice Extent from Reanalysis</t>
+          <t>Arctic Monthly Mean Sea Ice Extent from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent_obs.png</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -15725,7 +15713,7 @@
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1979-01-01</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -15735,12 +15723,12 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>[-180, 0, 180, 90]</t>
+          <t>[-180, 60, 180, 90]</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1979-01-01T00:00:00.000Z', '2025-05-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -15752,17 +15740,17 @@
         <v>0</v>
       </c>
       <c r="O201" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -15774,17 +15762,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Arctic Monthly Mean Sea Ice Extent from Observations Reprocessing</t>
+          <t>Arctic Freshwater Content from Reanalysis</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_TEMPSAL_FWC.png</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -15797,7 +15785,7 @@
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
-          <t>1979-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -15807,34 +15795,34 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>[-180, 60, 180, 90]</t>
+          <t>[-180, 62, 180, 90]</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>['1979-01-01T00:00:00.000Z', '2025-05-05T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2017-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>['Sea ice']</t>
+          <t>['Salinity']</t>
         </is>
       </c>
       <c r="N202" t="b">
         <v>0</v>
       </c>
       <c r="O202" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_TEMPSAL_FWC-hq.png</t>
         </is>
       </c>
     </row>
@@ -15846,30 +15834,30 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Arctic Freshwater Content from Reanalysis</t>
+          <t>Black Sea Oxygen Trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_TEMPSAL_FWC.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_HEALTH_oxygen_trend.png</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['In-situ observations']</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>['Arctic Ocean']</t>
+          <t>['Black Sea']</t>
         </is>
       </c>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1955-01-01</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -15877,36 +15865,32 @@
           <t>['Monthly']</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>[-180, 62, 180, 90]</t>
-        </is>
-      </c>
+      <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2017-12-31T00:00:00.000Z']</t>
+          <t>['1955-01-01T00:00:00.000Z', '2021-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>['Salinity']</t>
+          <t>['Oxygen']</t>
         </is>
       </c>
       <c r="N203" t="b">
         <v>0</v>
       </c>
       <c r="O203" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>2017-12-31</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_TEMPSAL_FWC-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_HEALTH_oxygen_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -15918,17 +15902,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Black Sea Oxygen Trend from Observations Reprocessing</t>
+          <t>Black Sea Significant Wave Height extreme from Reanalysis</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_HEALTH_oxygen_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly.png</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>['In-situ observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -15937,44 +15921,52 @@
           <t>['Black Sea']</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.028, 'units': 'degree'}, 'column': {'magnitude': 0.037, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
-          <t>1955-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr"/>
+          <t>['Yearly']</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>[27.37006950378418, 40.86015319824219, 41.9622917175293, 46.80458068847656]</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>['1955-01-01T00:00:00.000Z', '2021-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>['Oxygen']</t>
+          <t>['Wave']</t>
         </is>
       </c>
       <c r="N204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O204" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P204" t="inlineStr"/>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>2021-12-31</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_HEALTH_oxygen_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -15986,12 +15978,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Black Sea Significant Wave Height extreme from Reanalysis</t>
+          <t>Black Sea Surface Temperature extreme from Reanalysis</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly.png</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -16023,7 +16015,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>[27.37006950378418, 40.86015319824219, 41.9622917175293, 46.80458068847656]</t>
+          <t>[27.25, 40.5, 42, 47]</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -16033,7 +16025,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>['Wave']</t>
+          <t>['Temperature']</t>
         </is>
       </c>
       <c r="N205" t="b">
@@ -16050,7 +16042,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -16062,17 +16054,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Black Sea Surface Temperature extreme from Reanalysis</t>
+          <t>Black Sea Surface Temperature time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -16081,30 +16073,26 @@
           <t>['Black Sea']</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.028, 'units': 'degree'}, 'column': {'magnitude': 0.037, 'units': 'degree'}}</t>
-        </is>
-      </c>
+      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>[27.25, 40.5, 42, 47]</t>
+          <t>[26.38, 38.73, 42.38, 48.78]</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -16113,20 +16101,16 @@
         </is>
       </c>
       <c r="N206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>2</v>
       </c>
       <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>2023-12-31</t>
-        </is>
-      </c>
+      <c r="Q206" t="inlineStr"/>
       <c r="R206" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -16138,12 +16122,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Black Sea Surface Temperature time series and trend from Observations Reprocessing</t>
+          <t>Black Sea Surface Temperature trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_trend.png</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -16157,7 +16141,11 @@
           <t>['Black Sea']</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
@@ -16166,12 +16154,12 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>[26.38, 38.73, 42.38, 48.78]</t>
+          <t>[26.375, 38.724998474121094, 42.375, 48.775001525878906]</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -16185,7 +16173,7 @@
         </is>
       </c>
       <c r="N207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
         <v>2</v>
@@ -16194,7 +16182,7 @@
       <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -16206,49 +16194,45 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Black Sea Surface Temperature trend map from Observations Reprocessing</t>
+          <t>Nino 3.4 Temporal Evolution of Vertical Profile of Temperature from Reanalysis</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_Tzt_anomaly.png</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>['Black Sea']</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
-        </is>
-      </c>
+          <t>['Global Ocean']</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>[26.375, 38.724998474121094, 42.375, 48.775001525878906]</t>
+          <t>[-170, -5, -120, 5]</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', None]</t>
+          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -16257,16 +16241,20 @@
         </is>
       </c>
       <c r="N208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_Tzt_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -16278,12 +16266,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Nino 3.4 Temporal Evolution of Vertical Profile of Temperature from Reanalysis</t>
+          <t>Nino 3.4 Sea Surface Temperature time series from Reanalysis</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_Tzt_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_sst_area_averaged_anomaly.png</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -16328,7 +16316,7 @@
         <v>0</v>
       </c>
       <c r="O209" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P209" t="inlineStr"/>
       <c r="Q209" t="inlineStr">
@@ -16338,7 +16326,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_Tzt_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_sst_area_averaged_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -16350,17 +16338,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Nino 3.4 Sea Surface Temperature time series from Reanalysis</t>
+          <t>Global Ocean Yearly CO2 Sink from Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_sst_area_averaged_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_co2_flux_integrated.png</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['In-situ observations']</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -16373,44 +16361,40 @@
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>[-170, -5, -120, 5]</t>
+          <t>[-180, -90, 180, 90]</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>['Temperature']</t>
+          <t>['Carbonate system']</t>
         </is>
       </c>
       <c r="N210" t="b">
         <v>0</v>
       </c>
       <c r="O210" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr">
-        <is>
-          <t>2023-12-31</t>
-        </is>
-      </c>
+      <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_sst_area_averaged_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_co2_flux_integrated-hq.png</t>
         </is>
       </c>
     </row>
@@ -16422,12 +16406,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Global Ocean Yearly CO2 Sink from Multi-Observations Reprocessing</t>
+          <t>Global Ocean acidification - mean sea water pH time series and trend from Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_co2_flux_integrated.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_area_averaged.png</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -16478,7 +16462,7 @@
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_co2_flux_integrated-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_area_averaged-hq.png</t>
         </is>
       </c>
     </row>
@@ -16490,12 +16474,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Global Ocean acidification - mean sea water pH time series and trend from Multi-Observations Reprocessing</t>
+          <t>Global ocean acidification - mean sea water pH trend map from Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_area_averaged.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_trend.png</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -16518,12 +16502,12 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Multi-yearly']</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>[-180, -90, 180, 90]</t>
+          <t>[-179.875, -88.125, 179.875, 89.875]</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -16537,7 +16521,7 @@
         </is>
       </c>
       <c r="N212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O212" t="n">
         <v>2</v>
@@ -16546,7 +16530,7 @@
       <c r="Q212" t="inlineStr"/>
       <c r="R212" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_area_averaged-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -16558,17 +16542,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Global ocean acidification - mean sea water pH trend map from Multi-Observations Reprocessing</t>
+          <t>Atlantic Meridional Overturning Circulation AMOC profile at 26N from Reanalysis</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_26N_profile.png</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>['In-situ observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -16581,7 +16565,7 @@
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
-          <t>1985-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -16589,32 +16573,32 @@
           <t>['Multi-yearly']</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>[-179.875, -88.125, 179.875, 89.875]</t>
-        </is>
-      </c>
+      <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', None]</t>
+          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>['Carbonate system']</t>
+          <t>['Velocity']</t>
         </is>
       </c>
       <c r="N213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_26N_profile-hq.png</t>
         </is>
       </c>
     </row>
@@ -16626,12 +16610,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Atlantic Meridional Overturning Circulation AMOC profile at 26N from Reanalysis</t>
+          <t>Atlantic Meridional Overturning Circulation AMOC timeseries at 26N from Reanalysis</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_26N_profile.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_max26N_timeseries.png</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -16654,7 +16638,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>['Multi-yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -16682,7 +16666,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_26N_profile-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_max26N_timeseries-hq.png</t>
         </is>
       </c>
     </row>
@@ -16694,17 +16678,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Atlantic Meridional Overturning Circulation AMOC timeseries at 26N from Reanalysis</t>
+          <t>Global Ocean Sea Surface Temperature time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_max26N_timeseries.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -16717,7 +16701,7 @@
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -16725,32 +16709,32 @@
           <t>['Monthly']</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>[-180, -90, 180, 90]</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>['Velocity']</t>
+          <t>['Temperature']</t>
         </is>
       </c>
       <c r="N215" t="b">
         <v>0</v>
       </c>
       <c r="O215" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr">
-        <is>
-          <t>2023-12-31</t>
-        </is>
-      </c>
+      <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_max26N_timeseries-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -16762,12 +16746,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Global Ocean Sea Surface Temperature time series and trend from Observations Reprocessing</t>
+          <t>Global Ocean Sea Surface Temperature trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_trend.png</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -16781,7 +16765,11 @@
           <t>['Global Ocean']</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
@@ -16790,12 +16778,12 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>[-180, -90, 180, 90]</t>
+          <t>[-179.97500610351562, -89.9749984741211, 179.97500610351562, 89.97500610351562]</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16809,16 +16797,16 @@
         </is>
       </c>
       <c r="N216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P216" t="inlineStr"/>
       <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -16830,17 +16818,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Global Ocean Sea Surface Temperature trend map from Observations Reprocessing</t>
+          <t>Mean Heat Transport across sections from Reanalysis</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_heattrp.png</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -16849,48 +16837,48 @@
           <t>['Global Ocean']</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
-        </is>
-      </c>
+      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Multi-yearly', 'Yearly']</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>[-179.97500610351562, -89.9749984741211, 179.97500610351562, 89.97500610351562]</t>
+          <t>[-180, -90, 180, 90]</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', None]</t>
+          <t>['1993-01-01T00:00:00.000Z', '2017-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>['Temperature']</t>
+          <t>['Velocity']</t>
         </is>
       </c>
       <c r="N217" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>2017-12-31</t>
+        </is>
+      </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_heattrp-hq.png</t>
         </is>
       </c>
     </row>
@@ -16902,12 +16890,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Mean Heat Transport across sections from Reanalysis</t>
+          <t>Northward Heat Transport for Global Ocean, Atlantic and Indian+Pacific basins from Reanalysis</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_heattrp.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_northward_mht.png</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -16952,7 +16940,7 @@
         <v>0</v>
       </c>
       <c r="O218" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="inlineStr">
@@ -16962,7 +16950,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_heattrp-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_northward_mht-hq.png</t>
         </is>
       </c>
     </row>
@@ -16974,12 +16962,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Northward Heat Transport for Global Ocean, Atlantic and Indian+Pacific basins from Reanalysis</t>
+          <t>Mean Volume Transport across sections from Reanalysis</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_northward_mht.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_voltrp.png</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -17024,7 +17012,7 @@
         <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="P219" t="inlineStr"/>
       <c r="Q219" t="inlineStr">
@@ -17034,7 +17022,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_northward_mht-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_voltrp-hq.png</t>
         </is>
       </c>
     </row>
@@ -17046,12 +17034,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Mean Volume Transport across sections from Reanalysis</t>
+          <t>Iberia Biscay Ireland Coastal Upwelling Index from Reanalysis</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_voltrp.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_CURRENTS_cui.png</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -17062,7 +17050,7 @@
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>['Global Ocean']</t>
+          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G220" t="inlineStr"/>
@@ -17074,39 +17062,39 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>['Multi-yearly', 'Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>[-180, -90, 180, 90]</t>
+          <t>[-19, 26, 5, 42]</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2017-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2021-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>['Velocity']</t>
+          <t>['Temperature']</t>
         </is>
       </c>
       <c r="N220" t="b">
         <v>0</v>
       </c>
       <c r="O220" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P220" t="inlineStr"/>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>2017-12-31</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_voltrp-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_CURRENTS_cui-hq.png</t>
         </is>
       </c>
     </row>
@@ -17118,12 +17106,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Iberia Biscay Ireland Coastal Upwelling Index from Reanalysis</t>
+          <t>Iberia Biscay Ireland Significant Wave Height extreme from Reanalysis</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_CURRENTS_cui.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly.png</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -17137,48 +17125,52 @@
           <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.01, 'units': 'degree'}, 'column': {'magnitude': 0.01, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>[-19, 26, 5, 42]</t>
+          <t>[-19, 26, 5.000736236572266, 56.000919342041016]</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2021-08-01T00:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>['Temperature']</t>
+          <t>['Wave']</t>
         </is>
       </c>
       <c r="N221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O221" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P221" t="inlineStr"/>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_CURRENTS_cui-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -17190,12 +17182,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Iberia Biscay Ireland Significant Wave Height extreme from Reanalysis</t>
+          <t>Iberia Biscay Ireland Strong Wave Incidence index from Reanalysis</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_swi.png</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -17222,7 +17214,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -17232,7 +17224,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2025-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -17244,17 +17236,17 @@
         <v>1</v>
       </c>
       <c r="O222" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_swi-hq.png</t>
         </is>
       </c>
     </row>
@@ -17266,17 +17258,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Iberia Biscay Ireland Strong Wave Incidence index from Reanalysis</t>
+          <t>Mediterrranean Outflow Water Index from Reanalysis &amp; Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_swi.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_WMHE_mow.png</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['In-situ observations', 'Numerical models']</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -17285,15 +17277,11 @@
           <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.01, 'units': 'degree'}, 'column': {'magnitude': 0.01, 'units': 'degree'}}</t>
-        </is>
-      </c>
+      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
-          <t>1980-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -17303,34 +17291,34 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>[-19, 26, 5.000736236572266, 56.000919342041016]</t>
+          <t>[-19, 26, 5, 56]</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2025-04-30T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2021-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>['Wave']</t>
+          <t>['Salinity']</t>
         </is>
       </c>
       <c r="N223" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="P223" t="inlineStr"/>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_swi-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_WMHE_mow-hq.png</t>
         </is>
       </c>
     </row>
@@ -17342,26 +17330,30 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Mediterrranean Outflow Water Index from Reanalysis &amp; Multi-Observations Reprocessing</t>
+          <t>Mediterranean Sea Significant Wave Height extreme from Reanalysis</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_WMHE_mow.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly.png</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>['In-situ observations', 'Numerical models']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr"/>
+          <t>['Mediterranean Sea']</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.042, 'units': 'degree'}, 'column': {'magnitude': 0.042, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
@@ -17370,39 +17362,39 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>[-19, 26, 5, 56]</t>
+          <t>[-18.125, 30.1875, 36.29166793823242, 45.97916793823242]</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2021-08-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2020-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>['Salinity']</t>
+          <t>['Wave']</t>
         </is>
       </c>
       <c r="N224" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O224" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="P224" t="inlineStr"/>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_WMHE_mow-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -17414,12 +17406,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Mediterranean Sea Significant Wave Height extreme from Reanalysis</t>
+          <t>Mediterranean Sea Surface Temperature extreme from Reanalysis</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly.png</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -17451,7 +17443,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>[-18.125, 30.1875, 36.29166793823242, 45.97916793823242]</t>
+          <t>[-17.29166603088379, 30.1875, 36.29166793823242, 45.97916793823242]</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -17461,7 +17453,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>['Wave']</t>
+          <t>['Temperature']</t>
         </is>
       </c>
       <c r="N225" t="b">
@@ -17478,7 +17470,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -17490,17 +17482,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Mediterranean Sea Surface Temperature extreme from Reanalysis</t>
+          <t>Mediterranean Sea Surface Temperature time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -17509,30 +17501,26 @@
           <t>['Mediterranean Sea']</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.042, 'units': 'degree'}, 'column': {'magnitude': 0.042, 'units': 'degree'}}</t>
-        </is>
-      </c>
+      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>[-17.29166603088379, 30.1875, 36.29166793823242, 45.97916793823242]</t>
+          <t>[5.56, 30.13, 36.33, 46.03]</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2020-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -17541,20 +17529,16 @@
         </is>
       </c>
       <c r="N226" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>2</v>
       </c>
       <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr">
-        <is>
-          <t>2020-12-31</t>
-        </is>
-      </c>
+      <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -17566,12 +17550,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Mediterranean Sea Surface Temperature time series and trend from Observations Reprocessing</t>
+          <t>Mediterranean Sea Surface Temperature trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_trend.png</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -17585,7 +17569,11 @@
           <t>['Mediterranean Sea']</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
@@ -17594,12 +17582,12 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>[5.56, 30.13, 36.33, 46.03]</t>
+          <t>[-5.563465118408203, 30.125, 36.32500076293945, 46.025001525878906]</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17613,7 +17601,7 @@
         </is>
       </c>
       <c r="N227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O227" t="n">
         <v>2</v>
@@ -17622,7 +17610,7 @@
       <c r="Q227" t="inlineStr"/>
       <c r="R227" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -17634,49 +17622,49 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Mediterranean Sea Surface Temperature trend map from Observations Reprocessing</t>
+          <t>North West Shelf Sea Surface Temperature extreme from Reanalysis</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/NORTHWESTSHELF_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly.png</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>['Mediterranean Sea']</t>
+          <t>['Atlantic: NW European Shelf', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
+          <t>{'row': {'magnitude': 0.013, 'units': 'degree'}, 'column': {'magnitude': 0.03, 'units': 'degree'}}</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>[-5.563465118408203, 30.125, 36.32500076293945, 46.025001525878906]</t>
+          <t>[-16, 46, 13, 62.74324035644531]</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', None]</t>
+          <t>['2020-01-01T00:00:00.000Z', '2020-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -17691,10 +17679,14 @@
         <v>2</v>
       </c>
       <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>2020-12-31</t>
+        </is>
+      </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/NORTHWESTSHELF_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -17706,71 +17698,67 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>North West Shelf Sea Surface Temperature extreme from Reanalysis</t>
+          <t>Gulf Stream destabilization point</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/NORTHWESTSHELF_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_ATLANTIC_gulf_stream_destabilization_point.png</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr"/>
+          <t>['Satellite observations']</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>['Atlantic: NW European Shelf', 'Atlantic: North']</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.013, 'units': 'degree'}, 'column': {'magnitude': 0.03, 'units': 'degree'}}</t>
-        </is>
-      </c>
+          <t>['Global Ocean']</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t>['Yearly']</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>[50, 40, 80, 45]</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>['1993-01-01T00:00:00.000Z', None]</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>[-16, 46, 13, 62.74324035644531]</t>
-        </is>
-      </c>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t>['2020-01-01T00:00:00.000Z', '2020-12-31T00:00:00.000Z']</t>
-        </is>
-      </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>['Temperature']</t>
-        </is>
-      </c>
       <c r="N229" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>2</v>
       </c>
       <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr">
-        <is>
-          <t>2020-12-31</t>
-        </is>
-      </c>
+      <c r="Q229" t="inlineStr"/>
       <c r="R229" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/NORTHWESTSHELF_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_ATLANTIC_gulf_stream_destabilization_point-hq.png</t>
         </is>
       </c>
     </row>
@@ -18258,7 +18246,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OFC_BALTIC_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_BALTIC_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -18275,7 +18263,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_OHC_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_BALTIC_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -18330,7 +18318,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OFC_BALTIC_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_BALTIC_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -20522,7 +20510,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/omi_climate_tempsal_ibi_extreme_var_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_TEMPSAL_IBI_extreme_var_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -23345,74 +23333,6 @@
           <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_TEMPSALOXY_BALTIC_mbi_sto2tz_gotland-hq.png</t>
         </is>
       </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>CMEMS</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Gulf Stream destabilization point</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_ATLANTIC_gulf_stream_destabilization_point.png</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>['Satellite observations']</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>['Global Ocean']</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr"/>
-      <c r="H308" t="inlineStr"/>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>1993-01-01</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>['Yearly']</t>
-        </is>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>[50, 40, 80, 45]</t>
-        </is>
-      </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t>['1993-01-01T00:00:00.000Z', None]</t>
-        </is>
-      </c>
-      <c r="M308" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="N308" t="b">
-        <v>0</v>
-      </c>
-      <c r="O308" t="n">
-        <v>2</v>
-      </c>
-      <c r="P308" t="inlineStr"/>
-      <c r="Q308" t="inlineStr"/>
-      <c r="R308" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-04-21T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-04-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-04-21T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-04-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-04-20T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-04-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-24T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-01-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-04-20T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-04-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-04-12T23:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-04-25T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-04-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-04-18T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-04-25T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-19T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-04-27T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>['1991-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
+          <t>['1991-01-01T00:00:00.000Z', '2026-01-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-04-20T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-04-27T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-04-20T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-04-27T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-04-19T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-04-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-04-20T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-04-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-04-21T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-04-28T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-04-20T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-04-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2023-11-22</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-04-21T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-04-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-04-20T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-04-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-04-20T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-04-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-04-21T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-04-28T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-04-20T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-04-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>['1987-01-01T00:00:00.000Z', '2026-02-28T23:00:00.000Z']</t>
+          <t>['1987-01-01T00:00:00.000Z', '2026-03-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-02-28T23:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-03-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-04-17T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-04-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-04-11T17:20:49.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-04-18T17:59:14.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-04-12T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-04-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-04-11T14:50:30.039Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-04-18T15:09:11.000Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-04-12T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-04-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2023-04-25T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2023-04-18T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2023-04-18T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2023-04-29T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-04T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-04-03T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-04-10T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-04-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-10T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-04-10T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-04-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-04-06T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-04-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-04-11T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-04-18T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-04-10T20:55:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-04-18T08:30:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-04-11T21:22:02.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-04-18T22:15:41.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2025-09-29T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-04-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -10906,7 +10906,7 @@
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>['1995-09-15T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['1995-09-15T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-04-10T23:29:19.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-04-17T23:54:45.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-04-10T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-04-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-07T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-07T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-07T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-07T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-07T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>['1991-08-01T00:00:00.000Z', '2025-11-30T00:00:00.000Z']</t>
+          <t>['1991-08-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>['1994-06-01T00:00:00.000Z', '2025-11-20T23:00:00.000Z']</t>
+          <t>['1994-06-01T00:00:00.000Z', '2025-12-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>['1994-07-01T00:00:00.000Z', '2025-11-01T00:00:00.000Z']</t>
+          <t>['1994-07-01T00:00:00.000Z', '2025-12-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-04-11T22:08:08.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-04-18T22:14:33.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2024-03-26T00:00:00.000Z', '2026-04-21T21:00:00.000Z']</t>
+          <t>['2024-03-26T00:00:00.000Z', '2026-04-28T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-04-11T05:23:26.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-04-18T08:45:56.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-11T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-18T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-04-11T23:40:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-04-18T23:40:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-04-11T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-04-18T22:28:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-03-30T12:00:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-04-18T17:43:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-11T23:11:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-18T23:15:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-11T21:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-18T21:14:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-11T23:40:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-18T23:40:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-04-10T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-04-17T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-05T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-04-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-10T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-05T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-04-28T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-05-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-04-28T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-05-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-04-27T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-04-27T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-05-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-04-25T11:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-04-28T10:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-04-27T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-05-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-04-25T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-05-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-27T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-03T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-04-27T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-05-04T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-04-27T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-05-04T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-04-26T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>['1980-01-01T01:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['1980-01-01T01:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-04-27T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-05-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-04-28T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-05-05T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-04-27T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-05-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>['1992-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['1992-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-04-28T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-05-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-04-27T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-05-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-04-27T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-05-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-04-28T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-05-05T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-04-27T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-05-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>['1999-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['1999-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-04-24T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-05-01T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-04-18T17:59:14.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-04-25T17:07:31.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-04-19T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-04-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-04-18T15:09:11.000Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-04-25T15:49:33.000Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-04-19T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-04-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2026-04-04T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2023-04-25T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2026-04-07T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2023-04-18T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2026-04-05T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>['2024-08-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['2026-03-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2026-04-13T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2025-07-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-16T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2023-04-29T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2026-04-13T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-11T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-06T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-04-10T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-06T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-04-17T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-04-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-17T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-04-17T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-04-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-03-10T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-04-12T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-04-18T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-04-25T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-04-18T08:30:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-04-24T20:55:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-04-18T22:15:41.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-04-25T23:11:36.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-04-02T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-04-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-04-17T23:54:45.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-04-24T23:03:48.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-04-17T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-04-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-04-18T22:14:33.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-04-25T23:07:24.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2024-03-26T00:00:00.000Z', '2026-04-28T21:00:00.000Z']</t>
+          <t>['2024-03-26T00:00:00.000Z', '2026-04-30T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-04-18T08:45:56.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-04-25T06:14:03.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-18T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-25T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-04-18T23:40:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-04-25T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-04-18T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-04-25T22:28:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-04-18T17:43:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-04-25T19:46:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-18T23:15:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-24T23:14:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-18T21:14:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-25T21:13:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-18T23:40:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-26T00:24:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-04-17T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-04-24T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-12T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-17T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-12T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-05-05T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-05-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-05-05T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-05-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-05-04T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-05-11T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-04-28T10:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-05-08T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-05-04T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-05-02T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-05-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-03T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-11T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-05-04T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-05-11T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-05-04T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-05-11T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-05-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-05-04T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-05-05T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-05-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-05-04T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-05-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2604,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-05-05T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-05-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-05-04T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-05-11T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-05-04T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-05-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-05-05T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-05-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-05-04T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3532,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-05-01T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-05-08T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-04-25T17:07:31.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-05-02T17:46:31.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-04-26T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-04-25T15:49:33.000Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-05-02T16:38:57.000Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-04-26T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-04-04T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2026-04-13T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-04-07T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2026-04-13T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2026-02-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-04-05T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2026-04-23T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>['2026-03-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['2026-04-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-04-13T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2026-04-16T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-07-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2025-07-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-23T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-04-13T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2026-04-22T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7402,7 +7402,7 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-13T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8010,7 +8010,7 @@
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-04-17T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-13T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8162,7 +8162,7 @@
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-04-24T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-05-01T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-24T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-04-24T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-05-01T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-03-22T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-04-25T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-05-02T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-04-24T20:55:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-05-02T07:30:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-04-25T23:11:36.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-05-02T23:03:37.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-04-09T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-04-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-04-24T23:03:48.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-05-01T23:29:21.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-04-24T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-05-01T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>['Hourly', 'Daily']</t>
+          <t>['Hourly']</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-04-25T23:07:24.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-05-02T21:33:15.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-04-25T06:14:03.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-05-02T07:21:33.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-25T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-02T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-04-25T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-02T23:40:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-04-25T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-02T22:28:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-04-25T19:46:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-02T19:30:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-24T23:14:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-02T23:59:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-25T21:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-02T21:17:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-26T00:24:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-02T23:55:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-04-24T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-05-01T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-19T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-04-08T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-04-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-24T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-01T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-19T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-05-12T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-05-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-05-12T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-05-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-01-31T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-02-28T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-05-11T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-05-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-05-08T23:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-05-12T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-05-09T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-05-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-11T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-18T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-05-11T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-05-18T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-05-11T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-05-18T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-05-10T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-05-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-05-09T23:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-05-19T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-05-09T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-05-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>['1950-01-08T00:00:00.000Z', '2026-03-31T23:00:00.000Z']</t>
+          <t>['1950-01-08T00:00:00.000Z', '2026-04-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-05-12T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-05-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-05-11T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-05-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-12-23T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2025-11-18T23:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2025-12-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-12-23T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-05-09T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-05-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-05-09T23:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-05-19T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-05-08T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-05-15T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-01-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-05-02T17:46:31.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-05-09T15:34:37.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-05-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-05-02T16:38:57.000Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-05-09T15:07:32.294Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-05-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-04-13T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2026-04-16T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-04-13T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2026-04-22T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-02-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2026-02-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>['2020-01-08T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['2020-01-08T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-04-23T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2026-04-24T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>['2020-01-02T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['2020-01-02T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-04-16T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2026-04-25T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-07-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2025-07-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-04-22T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2026-05-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>['2020-01-04T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['2020-01-04T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-25T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-20T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-04-24T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-20T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-05-01T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-05-08T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-05-01T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-05-02T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-02T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-02T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-02T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-02T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-05-02T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-05-09T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-05-02T07:30:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-05-08T21:20:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-05-02T23:03:37.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-05-09T23:29:09.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-04-16T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-04-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>['1995-09-15T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
+          <t>['1995-09-15T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-05-01T23:29:21.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-05-08T23:52:44.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-05-01T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-05-08T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>['1991-08-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
+          <t>['1991-08-01T00:00:00.000Z', '2026-01-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>['1994-07-01T00:00:00.000Z', '2025-12-01T00:00:00.000Z']</t>
+          <t>['1994-07-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-05-02T21:33:15.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-05-09T22:39:05.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2024-03-26T00:00:00.000Z', '2026-04-30T21:00:00.000Z']</t>
+          <t>['2024-03-26T00:00:00.000Z', '2026-05-19T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>['2024-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['2024-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-05-02T07:21:33.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-05-09T08:09:22.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-02T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-09T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>['1979-12-11T04:00:00.000Z', '2025-06-30T23:00:00.000Z']</t>
+          <t>['1979-12-11T04:00:00.000Z', '2026-01-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-02T23:40:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-09T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-02T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-09T22:28:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-02T19:30:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-09T19:44:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-02T23:59:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-09T23:59:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-02T21:17:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-09T21:13:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-02T23:55:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-10T00:10:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-05-01T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-05-08T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-26T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-04-22T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-04-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-01T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-08T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-26T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-05-19T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-05-19T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-05-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-24T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-02-28T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-03-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-05-18T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-05-25T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-05-12T11:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-05-20T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-05-16T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-05-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-18T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-25T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-05-18T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-05-25T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-05-18T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-05-25T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-05-17T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-05-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-05-19T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-05-26T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-05-18T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-05-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>['1992-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['1992-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-05-19T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-05-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-05-18T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-05-25T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3068,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2025-12-23T23:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-02-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3144,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-05-18T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-05-25T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-05-19T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-05-26T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-05-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>['1987-01-01T00:00:00.000Z', '2026-03-31T23:00:00.000Z']</t>
+          <t>['1987-01-01T00:00:00.000Z', '2026-04-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-05-15T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-05-22T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-05-09T15:34:37.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-05-16T15:57:48.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-05-10T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-05-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-05-09T15:07:32.294Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-05-16T15:12:38.593Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-05-10T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-05-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-04-16T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2026-04-28T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-04-22T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2026-04-27T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-02-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2026-02-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-04-24T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2026-04-24T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-04-25T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2026-05-04T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-07-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2025-07-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-05-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2026-05-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-02T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-05-08T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-05-15T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-02T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-15T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-05-02T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-05-15T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-09T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-09T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-09T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-09T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-04-18T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-05-09T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-05-16T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-05-08T21:20:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-05-15T21:05:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-05-09T23:29:09.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-05-16T23:52:40.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-04-23T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>['2003-04-01T00:00:00.000Z', '2025-06-30T00:00:00.000Z']</t>
+          <t>['2003-04-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-05-08T23:52:44.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-05-15T23:44:40.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-05-08T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-05-15T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-09T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>['1994-06-01T00:00:00.000Z', '2025-12-21T23:00:00.000Z']</t>
+          <t>['1994-06-01T00:00:00.000Z', '2026-01-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-05-09T22:39:05.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-05-16T23:33:47.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2024-03-26T00:00:00.000Z', '2026-05-19T21:00:00.000Z']</t>
+          <t>['2024-03-26T00:00:00.000Z', '2026-05-28T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-05-09T08:09:22.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-05-16T09:05:37.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-09T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-16T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-09T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-16T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-09T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-16T22:28:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-09T19:44:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-16T19:44:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-09T23:59:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-16T23:59:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-09T21:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-16T22:16:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-10T00:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-16T14:10:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-05-08T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-05-15T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-04-29T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-05-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-08T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-15T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-03T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-06-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-05-26T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-06-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-05-25T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-06-01T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-05-20T11:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-05-28T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-05-23T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-05-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-25T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-01T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>['Monthly', 'Daily']</t>
+          <t>['Monthly', 'Daily', 'Yearly']</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>['1991-01-01T00:00:00.000Z', '2026-01-31T00:00:00.000Z']</t>
+          <t>['1991-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>['Sea ice']</t>
+          <t>['Temperature', 'Velocity', 'Mixed layer thickness', 'Sea ice']</t>
         </is>
       </c>
       <c r="N15" t="b">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-05-25T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-06-01T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-05-25T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-06-01T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-05-25T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-05-26T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-06-02T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-05-23T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-06-01T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-05-26T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-06-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-05-25T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-06-01T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-05-25T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-06-01T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-05-26T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-06-02T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-05-25T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-03-31T23:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-04-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>['1999-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['1999-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-05-22T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-05-29T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-05-16T15:57:48.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-05-23T15:33:00.334Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-05-17T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-05-16T15:12:38.593Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-05-23T15:16:16.103Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-05-17T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-04-28T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2026-04-28T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-04-27T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2026-05-07T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-02-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2026-02-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-04-24T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2026-05-13T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-05-04T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2026-05-13T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-07-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2025-07-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-05-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2026-05-10T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2024-12-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2025-12-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-04T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-05-08T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-04T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-05-15T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-05-22T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-15T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-22T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-05-15T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-05-22T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-16T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-16T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-16T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-16T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-05-16T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-05-23T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-05-15T21:05:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-05-23T10:15:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-05-16T23:52:40.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-05-23T23:44:28.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-05-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>['2003-04-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['2003-04-01T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-05-15T23:44:40.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-05-22T23:40:10.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-05-15T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-05-22T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-05-16T23:33:47.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-05-23T23:13:33.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2024-03-26T00:00:00.000Z', '2026-05-28T21:00:00.000Z']</t>
+          <t>['2024-03-26T00:00:00.000Z', '2026-05-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-05-16T09:05:37.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-05-18T16:38:26.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-16T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-23T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-16T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-23T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-16T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-23T22:28:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-16T19:44:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-23T19:19:59.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-16T23:59:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-23T23:59:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-16T22:16:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-23T21:11:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-16T14:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-23T23:55:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-05-15T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-05-22T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-10T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-15T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-22T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-10T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -18246,7 +18246,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_BALTIC_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OFC_BALTIC_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-06-02T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-06-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-06-02T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-06-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-06-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-06-01T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-06-08T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-05-28T11:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-06-08T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-05-30T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-06-07T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-01T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-07T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-06-01T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-06-08T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-06-01T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-06-08T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-06-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-06-02T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-06-09T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-06-01T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-06-08T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-06-02T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-06-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-06-01T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-06-08T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-03T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-03T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-06-01T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-06-08T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-06-02T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-06-09T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-05-29T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-06-05T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2025-12-31T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-01-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-05-23T15:33:00.334Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-05-30T15:52:30.662Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-05-23T15:16:16.103Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-05-30T15:19:52.969Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-04-28T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2026-05-10T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-05-07T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2026-05-12T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-02-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2026-02-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>['2020-01-08T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['2020-01-08T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-05-13T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2026-05-13T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>['2020-01-02T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['2020-01-02T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-05-13T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2026-05-15T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-07-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2025-07-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-05-10T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2026-05-19T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>['2020-01-04T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['2020-01-04T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-16T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-05-15T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-05-22T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-05-29T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-22T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-29T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-05-22T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-05-29T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-23T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-23T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-23T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-23T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-05-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-05-23T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-05-30T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-05-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-05-23T10:15:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-05-28T15:00:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-05-23T23:44:28.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-05-30T22:33:32.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-05-07T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-05-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-05-22T23:40:10.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-05-29T20:58:12.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-05-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-05-22T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-05-29T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-05-23T23:13:33.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-05-31T00:01:15.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-05-18T16:38:26.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-05-30T08:26:15.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-23T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-30T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>['2012-05-01T00:00:00.000Z', '2025-06-01T00:00:00.000Z']</t>
+          <t>['1960-01-01T00:00:00.000Z', '2025-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-23T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-30T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-23T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-30T22:28:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-23T19:19:59.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-05-30T19:44:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-23T23:59:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-31T00:10:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-23T21:11:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-30T23:17:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-23T23:55:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-31T00:10:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-05-22T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-05-29T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-17T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-05-06T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-05-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-22T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-17T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-06-09T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-06-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-06-09T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-06-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-06-09T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-06-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>['1998-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1998-01-01T00:00:00.000Z', '2025-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-06-08T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-06-15T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-06-08T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-06-11T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-06-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-06-07T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-06-13T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-07T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-15T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-06-08T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-06-15T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-06-08T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-06-15T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-06-07T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-06-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>['1980-01-01T01:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['1980-01-01T01:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-06-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-06-09T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-06-16T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-06-08T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-06-15T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-06-09T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-06-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-06-08T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-06-15T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-10T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-06-08T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-06-15T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-06-09T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-06-16T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-06-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-06-05T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-06-12T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-05-30T15:52:30.662Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-06-06T16:22:47.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-06-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-05-30T15:19:52.969Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-06-06T15:54:40.000Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-06-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-05-10T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2026-05-18T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-05-12T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2026-05-18T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-02-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2026-03-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>['2020-01-08T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['2020-01-08T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-05-13T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2026-05-13T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>['2026-04-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['2026-05-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>['2020-01-02T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['2020-01-02T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-05-15T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2026-05-22T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-07-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-05-19T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2026-05-28T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>['2020-01-04T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['2020-01-04T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2024-12-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2025-12-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-23T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-05-22T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-18T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-05-29T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-06-02T10:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-29T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-05-29T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-06-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-05T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-01-05T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-05-25T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-05-30T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-06-06T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-05-27T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-05-28T15:00:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-06-06T11:45:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-05-30T22:33:32.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-06-07T00:00:26.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-05-14T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-05-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>['2003-04-01T00:00:00.000Z', '2026-05-11T00:00:00.000Z']</t>
+          <t>['2003-04-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-05-29T20:58:12.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-06-05T23:55:08.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-05-27T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-05-29T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-06-05T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-05-31T00:01:15.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-06-07T00:03:08.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2024-03-26T00:00:00.000Z', '2026-05-31T21:00:00.000Z']</t>
+          <t>['2024-03-26T00:00:00.000Z', '2026-06-17T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-05-30T08:26:15.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-06-06T07:30:00.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-30T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-07T00:18:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>['1960-01-01T00:00:00.000Z', '2025-06-01T00:00:00.000Z']</t>
+          <t>['2012-05-01T00:00:00.000Z', '2025-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>['1821-05-25T05:00:00.000Z', '2024-12-31T23:59:59.000Z']</t>
+          <t>['1821-05-25T05:00:00.000Z', '2025-06-30T23:59:31.000Z']</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>[-180, -90, 179.99899291992188, 74.61699676513672]</t>
+          <t>[-180, -90, 179.99899291992188, 9.969209968386869e+36]</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>['1970-04-27T18:00:00.000Z', '2024-12-31T23:57:00.000Z']</t>
+          <t>['1970-04-27T18:00:00.000Z', '2025-06-30T23:59:00.000Z']</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-30T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-06-07T01:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-30T22:28:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-06-06T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-05-30T19:44:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-06-06T19:43:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-31T00:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-07T01:13:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-30T23:17:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-06T23:17:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-31T00:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-07T01:10:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-05-29T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-06-05T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-05-20T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-05-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-28T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-05T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-24T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-06-16T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-06-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-06-16T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-06-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-06-16T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-06-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-06-15T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-06-22T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-06-11T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-06-13T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-06-15T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-06-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-06-13T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-06-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-15T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-22T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-06-15T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-06-22T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-06-15T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-06-22T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-06-14T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-06-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-06-15T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-06-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-06-16T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-06-23T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-06-15T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-06-22T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>['1950-01-08T00:00:00.000Z', '2026-04-30T23:00:00.000Z']</t>
+          <t>['1950-01-08T00:00:00.000Z', '2026-05-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-06-16T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-06-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-06-15T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-06-22T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-10T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-02-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-06-15T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-06-22T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-06-16T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-06-22T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-06-15T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-06-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>['1987-01-01T00:00:00.000Z', '2026-04-30T23:00:00.000Z']</t>
+          <t>['1987-01-01T00:00:00.000Z', '2026-05-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-06-12T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-06-19T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-06-06T16:22:47.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-06-13T15:56:10.507Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-06-07T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-06-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-06-06T15:54:40.000Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-06-13T14:19:55.000Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-06-07T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-06-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-05-18T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2026-05-22T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-05-18T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2026-05-27T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-03-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2026-03-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-05-13T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2026-06-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-05-22T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2026-05-31T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-05-28T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2026-05-28T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-30T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-25T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-05-29T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-25T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2023-01-30T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-04T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-12T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-06-04T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-06-12T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-07T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-07T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-07T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-07T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-06-06T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-06-13T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-06-06T11:45:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-06-12T21:40:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-06-07T00:00:26.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-06-13T23:56:16.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-05-21T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-06-05T23:55:08.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-06-12T23:47:16.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-06-05T23:00:00.000Z']</t>
+          <t>['2023-11-20T00:00:00.000Z', '2026-06-12T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>['1991-08-01T00:00:00.000Z', '2026-01-31T00:00:00.000Z']</t>
+          <t>['1991-08-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>['1994-07-01T00:00:00.000Z', '2026-01-01T00:00:00.000Z']</t>
+          <t>['1994-07-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-06-07T00:03:08.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-06-13T22:21:10.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2024-03-26T00:00:00.000Z', '2026-06-17T21:00:00.000Z']</t>
+          <t>['2024-03-26T00:00:00.000Z', '2026-06-23T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>['2024-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['2024-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-06-06T07:30:00.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-06-13T07:44:03.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-07T00:18:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-13T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-06-07T01:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-06-13T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-06-06T22:27:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-06-13T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-06-06T19:43:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-06-11T22:00:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-07T01:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-14T00:10:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-06T23:17:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-13T21:10:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-07T01:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-14T00:10:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-06-05T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-06-12T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-05-27T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-06-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-05T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-12T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-06-23T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-06-23T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-06-23T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-28T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-03-31T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-04-30T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-06-22T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-06-29T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-06-13T23:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-06-23T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-06-22T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-06-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-06-21T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-06-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-22T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-29T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>['1991-01-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['1991-01-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-06-22T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-06-29T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-06-22T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-06-29T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-06-21T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-06-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-06-22T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-06-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-06-23T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-06-30T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-06-22T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-06-29T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>['1992-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['1992-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-06-23T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-06-22T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-06-29T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-06-22T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-06-29T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-06-22T23:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-06-30T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-06-22T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-06-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-04-30T23:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-05-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>['1999-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['1999-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-06-19T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-06-26T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-01-31T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-02-28T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-06-13T15:56:10.507Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-06-20T16:07:28.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-06-14T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-06-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-06-13T14:19:55.000Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-06-20T13:20:54.000Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-06-14T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-06-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-05-22T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2026-06-02T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-05-27T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2026-06-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-03-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2026-03-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-06-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2026-06-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-05-31T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2026-06-08T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-05-28T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2026-06-06T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-06T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-06-05T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-11T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2023-01-30T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-12T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-19T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-06-12T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-06-19T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-14T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-14T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-14T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-14T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-06-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-06-13T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-06-20T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-06-12T21:40:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-06-20T10:00:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-06-13T23:56:16.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-06-21T00:15:54.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-06-12T23:47:16.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-06-19T23:40:36.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2023-11-20T00:00:00.000Z', '2026-06-12T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-06-19T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>['1994-06-01T00:00:00.000Z', '2026-01-21T23:00:00.000Z']</t>
+          <t>['1994-06-01T00:00:00.000Z', '2026-02-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-06-13T22:21:10.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-06-20T22:44:24.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2024-03-26T00:00:00.000Z', '2026-06-23T21:00:00.000Z']</t>
+          <t>['2024-03-26T00:00:00.000Z', '2026-06-30T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-06-13T07:44:03.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-06-20T07:38:26.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-13T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-20T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2025-03-31T23:55:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-01-31T00:49:13.000Z']</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-06-13T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-06-20T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-06-13T22:27:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-06-20T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-06-11T22:00:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-06-20T19:44:59.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-14T00:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-21T00:14:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-13T21:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-20T21:13:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-14T00:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-21T00:10:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-06-12T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-06-19T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-07T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-06-03T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-06-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-12T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-19T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-07T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-07-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-07-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-06-29T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-07-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-06-23T11:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-06-29T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-06-29T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-06-27T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-07-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-29T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-06T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>[-180, 53, 180, 90]</t>
+          <t>[-179.985, 41.115, 179.98499999999996, 89.985]</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>['1964-01-01T00:00:00.000Z', '2025-03-31T00:00:00.000Z']</t>
+          <t>['1964-01-01T00:00:00.000Z', '2025-07-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-06-29T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-07-06T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-06-29T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-07-06T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-06-28T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-07-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>['1980-01-01T01:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['1980-01-01T01:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-06-29T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-06-30T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-07-07T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-06-29T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-07-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-07-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-06-29T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-07-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-24T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-02-24T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-06-29T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-07-06T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-06-30T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-07-07T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-06-29T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-06-26T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-07-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-06-20T16:07:28.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-06-27T15:59:55.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-06-21T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-06-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-06-20T13:20:54.000Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-06-27T14:06:39.000Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-06-21T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-06-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>['1992-10-13T00:32:22.000Z', '2025-10-18T23:50:14.000Z']</t>
+          <t>['1992-10-13T00:32:22.000Z', '2026-01-16T23:51:46.000Z']</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-10-18T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-01-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>['1992-10-13T05:51:26.000Z', '2025-10-18T23:42:44.000Z']</t>
+          <t>['1992-10-13T05:51:26.000Z', '2026-01-16T23:01:27.000Z']</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-10-18T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-01-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-06-02T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2026-06-03T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-06-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2026-06-11T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-03-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2026-03-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-06-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2026-06-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-06-08T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2026-06-16T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-06-06T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2026-06-15T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-13T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-06-12T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-08T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-19T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-26T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-06-19T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-06-26T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-21T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-21T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-21T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-21T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-06-15T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-06-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-06-20T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-06-27T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-06-20T10:00:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-06-26T20:20:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-06-21T00:15:54.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-06-28T00:43:22.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-06-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>['1995-09-15T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['1995-09-15T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-06-19T23:40:36.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-06-26T23:59:47.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-06-19T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-06-26T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-06-20T22:44:24.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-06-27T23:07:07.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-06-20T07:38:26.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-06-27T07:38:26.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-20T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-27T23:59:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-01-31T00:49:13.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-02-10T21:51:00.000Z']</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-06-20T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-06-27T23:10:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-06-20T22:27:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-06-27T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-06-20T19:44:59.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-06-26T18:42:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-21T00:14:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-28T00:15:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-20T21:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-27T21:13:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-21T00:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-28T00:10:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-06-19T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-06-26T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-14T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-06-10T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-06-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-19T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-26T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-14T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-07-07T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-07-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-07-07T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-07-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-07-06T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-07-13T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-06-29T11:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-07-07T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-07-04T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-07-11T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-06T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-13T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-07-06T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-07-13T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-07-06T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-07-13T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-07-05T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-07-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-07-07T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-07-14T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-07-06T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-07-13T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-07-07T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-07-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-07-06T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-07-13T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-17T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-02-03T23:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-03-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-17T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-07-06T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-07-13T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-07-07T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-07-14T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-07-03T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-07-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-06-27T15:59:55.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-07-04T15:52:00.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-06-28T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-07-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-06-27T14:06:39.000Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-07-04T13:54:59.427Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-06-28T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-07-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2025-05-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-01-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-06-03T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2026-06-15T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-06-11T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2026-06-16T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-03-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2026-04-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-06-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2026-06-20T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>['2026-05-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2026-06-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-06-16T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2026-06-16T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-06-15T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2026-06-24T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-20T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-15T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-06-19T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-15T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-26T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-06-26T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-07-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-05-28T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-06-22T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-06-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-06-27T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-07-04T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-06-26T20:20:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-07-03T15:00:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-06-28T00:43:22.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-07-04T20:16:00.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-06-11T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-06-26T23:59:47.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-07-03T23:57:07.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>['1980-11-03T00:00:00.000Z', '2025-06-04T00:00:00.000Z']</t>
+          <t>['1980-11-03T00:00:00.000Z', '2026-05-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-06-26T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-07-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-06-27T23:07:07.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-07-04T22:40:18.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2024-03-26T00:00:00.000Z', '2026-06-30T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-07-14T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13520,7 +13520,7 @@
         <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P171" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-06-27T07:38:26.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-07-03T04:07:30.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-27T23:59:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-04T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>['2012-05-01T00:00:00.000Z', '2025-06-01T00:00:00.000Z']</t>
+          <t>['1960-01-01T00:00:00.000Z', '2025-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -13742,7 +13742,7 @@
         <v>0</v>
       </c>
       <c r="O174" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P174" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-06-27T23:10:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-07-04T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-06-27T22:27:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-07-04T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-06-26T18:42:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-07-04T19:40:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-28T00:15:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-04T23:14:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-27T21:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-04T21:13:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-28T00:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-04T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-06-26T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-21T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-26T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-07-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-21T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R307"/>
+  <dimension ref="A1:R308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-07-14T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-07-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-07-14T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-07-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-07-13T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-07-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-07-07T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-07-16T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-07-11T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-07-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-13T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-20T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-07-13T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-07-20T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-07-13T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-07-20T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-07-12T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-07-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-07-14T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-07-21T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-07-13T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-07-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>['1950-01-08T00:00:00.000Z', '2026-05-31T23:00:00.000Z']</t>
+          <t>['1950-01-08T00:00:00.000Z', '2026-06-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-07-14T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-07-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-07-13T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-07-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-24T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-03-17T23:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-03-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-24T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-07-13T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-07-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-07-14T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-07-21T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-07-10T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-07-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-07-04T15:52:00.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-07-11T15:22:36.446Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4302,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-07-05T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-07-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-07-04T13:54:59.427Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-07-11T15:22:36.446Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4674,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-07-05T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-06-15T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2026-06-15T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-06-16T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2026-06-22T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-04-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2026-04-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>['2020-01-08T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2020-01-08T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-06-20T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2026-06-20T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>['2020-01-02T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2020-01-02T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-06-16T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2026-06-27T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-06-24T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2026-07-03T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>['2020-01-04T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2020-01-04T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-27T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-22T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-22T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-07-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-07-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-02T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-06-02T10:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-07-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-03T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-07-03T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-07-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>['1981-10-01T00:00:00.000Z', '2025-12-18T00:00:00.000Z']</t>
+          <t>['1981-10-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-04T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-06-29T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-07-04T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-07-11T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-07-03T15:00:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-07-11T08:40:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-07-04T20:16:00.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-07-11T23:54:46.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>['2003-04-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
+          <t>['2003-04-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-07-03T23:57:07.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-07-10T23:47:47.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="R147" t="inlineStr"/>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11754,7 +11754,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>928</v>
+        <v>1044</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-07-03T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-07-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>['1991-08-01T00:00:00.000Z', '2026-02-28T00:00:00.000Z']</t>
+          <t>['1991-08-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>['1994-06-01T00:00:00.000Z', '2026-02-18T23:00:00.000Z']</t>
+          <t>['1994-06-01T00:00:00.000Z', '2026-03-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>['1994-07-01T00:00:00.000Z', '2026-02-01T00:00:00.000Z']</t>
+          <t>['1994-07-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -12883,7 +12883,7 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-07-04T22:40:18.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-07-11T23:16:14.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12969,12 +12969,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>[-179, -89, 179, 89]</t>
+          <t>[-180, -89.5, 179.5, 89.5]</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-07-10T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -12986,7 +12986,7 @@
         <v>0</v>
       </c>
       <c r="O164" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P164" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>0</v>
       </c>
       <c r="O165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P165" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-07-14T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-07-22T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13286,7 +13286,7 @@
         <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P168" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>['2024-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['2024-06-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-07-03T04:07:30.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-07-11T07:24:22.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-04T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-11T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-07-04T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-07-11T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-07-04T22:27:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-07-11T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-07-04T19:40:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-07-11T18:38:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-04T23:14:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-11T23:13:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-04T21:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-11T21:10:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-04T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-11T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-28T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-03T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-07-02T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SSS SMOS/SMAP L4 OI - LOPS-v2023</t>
+          <t>SSS SMOS/SMAP L4 OI - LOPS-v2025</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>['2010-06-03T00:00:00.000Z', '2025-06-26T00:00:00.000Z']</t>
+          <t>['2010-06-03T00:00:00.000Z', '2025-12-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-28T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -15406,17 +15406,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Global coastal satellite derived bathymetry static</t>
+          <t>Northwestern Atlantic Ocean Physics and Ice Analysis and Forecast</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/BATHYMETRY_GLO_PHY_COASTAL_L4_MY_016_001.jpg</t>
+          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/NWATL_ANALYSISFORECAST_PHY_ICE_017_001.jpg</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -15431,36 +15431,46 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>{'row': {'magnitude': 100, 'units': 'm'}, 'column': {'magnitude': 100, 'units': 'm'}}</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
+          <t>{'row': {'magnitude': 0.027, 'units': 'degree'}, 'column': {'magnitude': 0.027, 'units': 'degree'}}</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>99</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Hourly']</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>[-179.99947916666667, -89.99947916666666, 179.99947916779914, 89.99947916654406]</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr"/>
+          <t>[-77, 34.88, -37.04000000000002, 54.46]</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>['2025-05-21T00:00:00.000Z', '2026-07-13T18:00:00.000Z']</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Temperature', 'Salinity', 'Sea surface height', 'Velocity', 'Mixed layer thickness', 'Sea ice']</t>
         </is>
       </c>
       <c r="N197" t="b">
         <v>0</v>
       </c>
       <c r="O197" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>{'basemapId': 'light', 'overlays': {'tags': []}}</t>
+          <t>{'basemapId': 'dark', 'overlays': {'tags': []}}</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr"/>
@@ -15474,69 +15484,65 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Antarctic Sea Ice Extent from Reanalysis</t>
+          <t>Global coastal satellite derived bathymetry static</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent.png</t>
+          <t>https://mdl-metadata.s3.waw3-1.cloudferro.com/metadata/thumbnails/BATHYMETRY_GLO_PHY_COASTAL_L4_MY_016_001.jpg</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr"/>
+          <t>['Satellite observations']</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>['Global Ocean', 'Antarctic Ocean']</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr"/>
+          <t>['Global Ocean']</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 100, 'units': 'm'}, 'column': {'magnitude': 100, 'units': 'm'}}</t>
+        </is>
+      </c>
       <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>1993-01-01</t>
-        </is>
-      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>[-180, -90, 180, 0]</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
-        </is>
-      </c>
+          <t>[-179.99947916666667, -89.99947916666666, 179.99947916779914, 89.99947916654406]</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
-          <t>['Sea ice']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="N198" t="b">
         <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>5</v>
-      </c>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>2023-12-31</t>
-        </is>
-      </c>
-      <c r="R198" t="inlineStr">
-        <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent-hq.png</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>{'basemapId': 'light', 'overlays': {'tags': []}}</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -15546,17 +15552,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Antarctic Monthly Sea Ice Extent from Observations Reprocessing</t>
+          <t>Antarctic Sea Ice Extent from Reanalysis</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent.png</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -15569,7 +15575,7 @@
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>1979-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -15584,7 +15590,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>['1979-01-01T00:00:00.000Z', '2025-05-05T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -15596,17 +15602,17 @@
         <v>0</v>
       </c>
       <c r="O199" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent-hq.png</t>
         </is>
       </c>
     </row>
@@ -15618,30 +15624,30 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Arctic Sea Ice Extent from Reanalysis</t>
+          <t>Antarctic Monthly Sea Ice Extent from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent_obs.png</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>['Arctic Ocean']</t>
+          <t>['Global Ocean', 'Antarctic Ocean']</t>
         </is>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1979-01-01</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -15651,12 +15657,12 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>[-180, 0, 180, 90]</t>
+          <t>[-180, -90, 180, 0]</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1979-01-01T00:00:00.000Z', '2025-05-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -15668,17 +15674,17 @@
         <v>0</v>
       </c>
       <c r="O200" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ANTARCTIC_OMI_SI_extent_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -15690,17 +15696,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Arctic Monthly Mean Sea Ice Extent from Observations Reprocessing</t>
+          <t>Arctic Sea Ice Extent from Reanalysis</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent.png</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -15713,7 +15719,7 @@
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>1979-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -15723,12 +15729,12 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>[-180, 60, 180, 90]</t>
+          <t>[-180, 0, 180, 90]</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>['1979-01-01T00:00:00.000Z', '2025-05-05T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -15740,17 +15746,17 @@
         <v>0</v>
       </c>
       <c r="O201" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent-hq.png</t>
         </is>
       </c>
     </row>
@@ -15762,17 +15768,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Arctic Freshwater Content from Reanalysis</t>
+          <t>Arctic Monthly Mean Sea Ice Extent from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_TEMPSAL_FWC.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent_obs.png</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -15785,7 +15791,7 @@
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1979-01-01</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -15795,34 +15801,34 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>[-180, 62, 180, 90]</t>
+          <t>[-180, 60, 180, 90]</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2017-12-31T00:00:00.000Z']</t>
+          <t>['1979-01-01T00:00:00.000Z', '2025-05-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>['Salinity']</t>
+          <t>['Sea ice']</t>
         </is>
       </c>
       <c r="N202" t="b">
         <v>0</v>
       </c>
       <c r="O202" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>2017-12-31</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_TEMPSAL_FWC-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_SI_extent_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -15834,30 +15840,30 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Black Sea Oxygen Trend from Observations Reprocessing</t>
+          <t>Arctic Freshwater Content from Reanalysis</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_HEALTH_oxygen_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_TEMPSAL_FWC.png</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>['In-situ observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>['Black Sea']</t>
+          <t>['Arctic Ocean']</t>
         </is>
       </c>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
-          <t>1955-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -15865,32 +15871,36 @@
           <t>['Monthly']</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>[-180, 62, 180, 90]</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>['1955-01-01T00:00:00.000Z', '2021-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2017-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>['Oxygen']</t>
+          <t>['Salinity']</t>
         </is>
       </c>
       <c r="N203" t="b">
         <v>0</v>
       </c>
       <c r="O203" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>2021-12-31</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_HEALTH_oxygen_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_TEMPSAL_FWC-hq.png</t>
         </is>
       </c>
     </row>
@@ -15902,17 +15912,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Black Sea Significant Wave Height extreme from Reanalysis</t>
+          <t>Black Sea Oxygen Trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_HEALTH_oxygen_trend.png</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['In-situ observations']</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -15921,52 +15931,44 @@
           <t>['Black Sea']</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.028, 'units': 'degree'}, 'column': {'magnitude': 0.037, 'units': 'degree'}}</t>
-        </is>
-      </c>
+      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1955-01-01</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>[27.37006950378418, 40.86015319824219, 41.9622917175293, 46.80458068847656]</t>
-        </is>
-      </c>
+          <t>['Monthly']</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1955-01-01T00:00:00.000Z', '2021-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>['Wave']</t>
+          <t>['Oxygen']</t>
         </is>
       </c>
       <c r="N204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P204" t="inlineStr"/>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_HEALTH_oxygen_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -15978,12 +15980,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Black Sea Surface Temperature extreme from Reanalysis</t>
+          <t>Black Sea Significant Wave Height extreme from Reanalysis</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly.png</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -16015,7 +16017,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>[27.25, 40.5, 42, 47]</t>
+          <t>[27.37006950378418, 40.86015319824219, 41.9622917175293, 46.80458068847656]</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -16025,7 +16027,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>['Temperature']</t>
+          <t>['Wave']</t>
         </is>
       </c>
       <c r="N205" t="b">
@@ -16042,7 +16044,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -16054,17 +16056,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Black Sea Surface Temperature time series and trend from Observations Reprocessing</t>
+          <t>Black Sea Surface Temperature extreme from Reanalysis</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly.png</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -16073,26 +16075,30 @@
           <t>['Black Sea']</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.028, 'units': 'degree'}, 'column': {'magnitude': 0.037, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>[26.38, 38.73, 42.38, 48.78]</t>
+          <t>[27.25, 40.5, 42, 47]</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', None]</t>
+          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -16101,16 +16107,20 @@
         </is>
       </c>
       <c r="N206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O206" t="n">
         <v>2</v>
       </c>
       <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -16122,12 +16132,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Black Sea Surface Temperature trend map from Observations Reprocessing</t>
+          <t>Black Sea Surface Temperature time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -16141,11 +16151,7 @@
           <t>['Black Sea']</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
-        </is>
-      </c>
+      <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
@@ -16154,12 +16160,12 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>[26.375, 38.724998474121094, 42.375, 48.775001525878906]</t>
+          <t>[26.38, 38.73, 42.38, 48.78]</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -16173,7 +16179,7 @@
         </is>
       </c>
       <c r="N207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>2</v>
@@ -16182,7 +16188,7 @@
       <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -16194,45 +16200,49 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Nino 3.4 Temporal Evolution of Vertical Profile of Temperature from Reanalysis</t>
+          <t>Black Sea Surface Temperature trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_Tzt_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_trend.png</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>['Global Ocean']</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr"/>
+          <t>['Black Sea']</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>[-170, -5, -120, 5]</t>
+          <t>[26.375, 38.724998474121094, 42.375, 48.775001525878906]</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -16241,20 +16251,16 @@
         </is>
       </c>
       <c r="N208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O208" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr">
-        <is>
-          <t>2023-12-31</t>
-        </is>
-      </c>
+      <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_Tzt_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BLKSEA_OMI_TEMPSAL_sst_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -16266,12 +16272,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Nino 3.4 Sea Surface Temperature time series from Reanalysis</t>
+          <t>Nino 3.4 Temporal Evolution of Vertical Profile of Temperature from Reanalysis</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_sst_area_averaged_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_Tzt_anomaly.png</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -16316,7 +16322,7 @@
         <v>0</v>
       </c>
       <c r="O209" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P209" t="inlineStr"/>
       <c r="Q209" t="inlineStr">
@@ -16326,7 +16332,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_sst_area_averaged_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_Tzt_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -16338,17 +16344,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Global Ocean Yearly CO2 Sink from Multi-Observations Reprocessing</t>
+          <t>Nino 3.4 Sea Surface Temperature time series from Reanalysis</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_co2_flux_integrated.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_sst_area_averaged_anomaly.png</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>['In-situ observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -16361,40 +16367,44 @@
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
-          <t>1985-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>[-180, -90, 180, 90]</t>
+          <t>[-170, -5, -120, 5]</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', None]</t>
+          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>['Carbonate system']</t>
+          <t>['Temperature']</t>
         </is>
       </c>
       <c r="N210" t="b">
         <v>0</v>
       </c>
       <c r="O210" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_co2_flux_integrated-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_CLIMVAR_enso_sst_area_averaged_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -16406,12 +16416,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Global Ocean acidification - mean sea water pH time series and trend from Multi-Observations Reprocessing</t>
+          <t>Global Ocean Yearly CO2 Sink from Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_area_averaged.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_co2_flux_integrated.png</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -16462,7 +16472,7 @@
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_area_averaged-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_co2_flux_integrated-hq.png</t>
         </is>
       </c>
     </row>
@@ -16474,12 +16484,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Global ocean acidification - mean sea water pH trend map from Multi-Observations Reprocessing</t>
+          <t>Global Ocean acidification - mean sea water pH time series and trend from Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_area_averaged.png</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -16502,12 +16512,12 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>['Multi-yearly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>[-179.875, -88.125, 179.875, 89.875]</t>
+          <t>[-180, -90, 180, 90]</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -16521,7 +16531,7 @@
         </is>
       </c>
       <c r="N212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O212" t="n">
         <v>2</v>
@@ -16530,7 +16540,7 @@
       <c r="Q212" t="inlineStr"/>
       <c r="R212" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_area_averaged-hq.png</t>
         </is>
       </c>
     </row>
@@ -16542,17 +16552,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Atlantic Meridional Overturning Circulation AMOC profile at 26N from Reanalysis</t>
+          <t>Global ocean acidification - mean sea water pH trend map from Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_26N_profile.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_trend.png</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['In-situ observations']</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -16565,7 +16575,7 @@
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -16573,32 +16583,32 @@
           <t>['Multi-yearly']</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>[-179.875, -88.125, 179.875, 89.875]</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>['Velocity']</t>
+          <t>['Carbonate system']</t>
         </is>
       </c>
       <c r="N213" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O213" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>2023-12-31</t>
-        </is>
-      </c>
+      <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_26N_profile-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_HEALTH_carbon_ph_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -16610,12 +16620,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Atlantic Meridional Overturning Circulation AMOC timeseries at 26N from Reanalysis</t>
+          <t>Atlantic Meridional Overturning Circulation AMOC profile at 26N from Reanalysis</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_max26N_timeseries.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_26N_profile.png</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -16638,7 +16648,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Multi-yearly']</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -16666,7 +16676,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_max26N_timeseries-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_26N_profile-hq.png</t>
         </is>
       </c>
     </row>
@@ -16678,17 +16688,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Global Ocean Sea Surface Temperature time series and trend from Observations Reprocessing</t>
+          <t>Atlantic Meridional Overturning Circulation AMOC timeseries at 26N from Reanalysis</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_max26N_timeseries.png</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -16701,7 +16711,7 @@
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -16709,32 +16719,32 @@
           <t>['Monthly']</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>[-180, -90, 180, 90]</t>
-        </is>
-      </c>
+      <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', None]</t>
+          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>['Temperature']</t>
+          <t>['Velocity']</t>
         </is>
       </c>
       <c r="N215" t="b">
         <v>0</v>
       </c>
       <c r="O215" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_NATLANTIC_amoc_max26N_timeseries-hq.png</t>
         </is>
       </c>
     </row>
@@ -16746,12 +16756,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Global Ocean Sea Surface Temperature trend map from Observations Reprocessing</t>
+          <t>Global Ocean Sea Surface Temperature time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -16765,11 +16775,7 @@
           <t>['Global Ocean']</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
-        </is>
-      </c>
+      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
@@ -16778,12 +16784,12 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>[-179.97500610351562, -89.9749984741211, 179.97500610351562, 89.97500610351562]</t>
+          <t>[-180, -90, 180, 90]</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16797,16 +16803,16 @@
         </is>
       </c>
       <c r="N216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P216" t="inlineStr"/>
       <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -16818,17 +16824,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Mean Heat Transport across sections from Reanalysis</t>
+          <t>Global Ocean Sea Surface Temperature trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_heattrp.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_trend.png</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -16837,48 +16843,48 @@
           <t>['Global Ocean']</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>['Multi-yearly', 'Yearly']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>[-180, -90, 180, 90]</t>
+          <t>[-179.97500610351562, -89.9749984741211, 179.97500610351562, 89.97500610351562]</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2017-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>['Velocity']</t>
+          <t>['Temperature']</t>
         </is>
       </c>
       <c r="N217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O217" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>2017-12-31</t>
-        </is>
-      </c>
+      <c r="Q217" t="inlineStr"/>
       <c r="R217" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_heattrp-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_TEMPSAL_sst_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16896,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Northward Heat Transport for Global Ocean, Atlantic and Indian+Pacific basins from Reanalysis</t>
+          <t>Mean Heat Transport across sections from Reanalysis</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_northward_mht.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_heattrp.png</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -16940,7 +16946,7 @@
         <v>0</v>
       </c>
       <c r="O218" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="inlineStr">
@@ -16950,7 +16956,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_northward_mht-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_heattrp-hq.png</t>
         </is>
       </c>
     </row>
@@ -16962,12 +16968,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Mean Volume Transport across sections from Reanalysis</t>
+          <t>Northward Heat Transport for Global Ocean, Atlantic and Indian+Pacific basins from Reanalysis</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_voltrp.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_northward_mht.png</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -17012,7 +17018,7 @@
         <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="P219" t="inlineStr"/>
       <c r="Q219" t="inlineStr">
@@ -17022,7 +17028,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_voltrp-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_northward_mht-hq.png</t>
         </is>
       </c>
     </row>
@@ -17034,12 +17040,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Iberia Biscay Ireland Coastal Upwelling Index from Reanalysis</t>
+          <t>Mean Volume Transport across sections from Reanalysis</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_CURRENTS_cui.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_voltrp.png</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -17050,7 +17056,7 @@
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
+          <t>['Global Ocean']</t>
         </is>
       </c>
       <c r="G220" t="inlineStr"/>
@@ -17062,39 +17068,39 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Multi-yearly', 'Yearly']</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>[-19, 26, 5, 42]</t>
+          <t>[-180, -90, 180, 90]</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2021-08-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2017-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>['Temperature']</t>
+          <t>['Velocity']</t>
         </is>
       </c>
       <c r="N220" t="b">
         <v>0</v>
       </c>
       <c r="O220" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P220" t="inlineStr"/>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2017-12-31</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_CURRENTS_cui-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/GLOBAL_OMI_WMHE_voltrp-hq.png</t>
         </is>
       </c>
     </row>
@@ -17106,12 +17112,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Iberia Biscay Ireland Significant Wave Height extreme from Reanalysis</t>
+          <t>Iberia Biscay Ireland Coastal Upwelling Index from Reanalysis</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_CURRENTS_cui.png</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -17125,52 +17131,48 @@
           <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.01, 'units': 'degree'}, 'column': {'magnitude': 0.01, 'units': 'degree'}}</t>
-        </is>
-      </c>
+      <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
-          <t>1980-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>[-19, 26, 5.000736236572266, 56.000919342041016]</t>
+          <t>[-19, 26, 5, 42]</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2021-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>['Wave']</t>
+          <t>['Temperature']</t>
         </is>
       </c>
       <c r="N221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P221" t="inlineStr"/>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_CURRENTS_cui-hq.png</t>
         </is>
       </c>
     </row>
@@ -17182,12 +17184,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Iberia Biscay Ireland Strong Wave Incidence index from Reanalysis</t>
+          <t>Iberia Biscay Ireland Significant Wave Height extreme from Reanalysis</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_swi.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly.png</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -17214,7 +17216,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -17224,7 +17226,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2025-04-30T00:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -17236,17 +17238,17 @@
         <v>1</v>
       </c>
       <c r="O222" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_swi-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -17258,17 +17260,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Mediterrranean Outflow Water Index from Reanalysis &amp; Multi-Observations Reprocessing</t>
+          <t>Iberia Biscay Ireland Strong Wave Incidence index from Reanalysis</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_WMHE_mow.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_swi.png</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>['In-situ observations', 'Numerical models']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -17277,11 +17279,15 @@
           <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.01, 'units': 'degree'}, 'column': {'magnitude': 0.01, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -17291,34 +17297,34 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>[-19, 26, 5, 56]</t>
+          <t>[-19, 26, 5.000736236572266, 56.000919342041016]</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2021-08-01T00:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2025-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>['Salinity']</t>
+          <t>['Wave']</t>
         </is>
       </c>
       <c r="N223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O223" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="P223" t="inlineStr"/>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_WMHE_mow-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_SEASTATE_swi-hq.png</t>
         </is>
       </c>
     </row>
@@ -17330,30 +17336,26 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Mediterranean Sea Significant Wave Height extreme from Reanalysis</t>
+          <t>Mediterrranean Outflow Water Index from Reanalysis &amp; Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_WMHE_mow.png</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['In-situ observations', 'Numerical models']</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>['Mediterranean Sea']</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.042, 'units': 'degree'}, 'column': {'magnitude': 0.042, 'units': 'degree'}}</t>
-        </is>
-      </c>
+          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
@@ -17362,39 +17364,39 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>[-18.125, 30.1875, 36.29166793823242, 45.97916793823242]</t>
+          <t>[-19, 26, 5, 56]</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2020-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2021-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>['Wave']</t>
+          <t>['Salinity']</t>
         </is>
       </c>
       <c r="N224" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="P224" t="inlineStr"/>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>2020-12-31</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/IBI_OMI_WMHE_mow-hq.png</t>
         </is>
       </c>
     </row>
@@ -17406,12 +17408,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Mediterranean Sea Surface Temperature extreme from Reanalysis</t>
+          <t>Mediterranean Sea Significant Wave Height extreme from Reanalysis</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly.png</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -17443,7 +17445,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>[-17.29166603088379, 30.1875, 36.29166793823242, 45.97916793823242]</t>
+          <t>[-18.125, 30.1875, 36.29166793823242, 45.97916793823242]</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -17453,7 +17455,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>['Temperature']</t>
+          <t>['Wave']</t>
         </is>
       </c>
       <c r="N225" t="b">
@@ -17470,7 +17472,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_SEASTATE_extreme_var_swh_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -17482,17 +17484,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Mediterranean Sea Surface Temperature time series and trend from Observations Reprocessing</t>
+          <t>Mediterranean Sea Surface Temperature extreme from Reanalysis</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly.png</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -17501,26 +17503,30 @@
           <t>['Mediterranean Sea']</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.042, 'units': 'degree'}, 'column': {'magnitude': 0.042, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>[5.56, 30.13, 36.33, 46.03]</t>
+          <t>[-17.29166603088379, 30.1875, 36.29166793823242, 45.97916793823242]</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', None]</t>
+          <t>['1993-01-01T00:00:00.000Z', '2020-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -17529,16 +17535,20 @@
         </is>
       </c>
       <c r="N226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O226" t="n">
         <v>2</v>
       </c>
       <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>2020-12-31</t>
+        </is>
+      </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -17550,12 +17560,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Mediterranean Sea Surface Temperature trend map from Observations Reprocessing</t>
+          <t>Mediterranean Sea Surface Temperature time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -17569,11 +17579,7 @@
           <t>['Mediterranean Sea']</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
-        </is>
-      </c>
+      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
@@ -17582,12 +17588,12 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>[-5.563465118408203, 30.125, 36.32500076293945, 46.025001525878906]</t>
+          <t>[5.56, 30.13, 36.33, 46.03]</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17601,7 +17607,7 @@
         </is>
       </c>
       <c r="N227" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>2</v>
@@ -17610,7 +17616,7 @@
       <c r="Q227" t="inlineStr"/>
       <c r="R227" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -17622,49 +17628,49 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>North West Shelf Sea Surface Temperature extreme from Reanalysis</t>
+          <t>Mediterranean Sea Surface Temperature trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/NORTHWESTSHELF_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_trend.png</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>['Atlantic: NW European Shelf', 'Atlantic: North']</t>
+          <t>['Mediterranean Sea']</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>{'row': {'magnitude': 0.013, 'units': 'degree'}, 'column': {'magnitude': 0.03, 'units': 'degree'}}</t>
+          <t>{'row': {'magnitude': 0.05, 'units': 'degree'}, 'column': {'magnitude': 0.05, 'units': 'degree'}}</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>[-16, 46, 13, 62.74324035644531]</t>
+          <t>[-5.563465118408203, 30.125, 36.32500076293945, 46.025001525878906]</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2020-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -17679,14 +17685,10 @@
         <v>2</v>
       </c>
       <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr">
-        <is>
-          <t>2020-12-31</t>
-        </is>
-      </c>
+      <c r="Q228" t="inlineStr"/>
       <c r="R228" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/NORTHWESTSHELF_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/MEDSEA_OMI_TEMPSAL_sst_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -17698,67 +17700,71 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Gulf Stream destabilization point</t>
+          <t>North West Shelf Sea Surface Temperature extreme from Reanalysis</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_ATLANTIC_gulf_stream_destabilization_point.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/NORTHWESTSHELF_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly.png</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
+          <t>['Numerical models']</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>['Global Ocean']</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr"/>
+          <t>['Atlantic: NW European Shelf', 'Atlantic: North']</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.013, 'units': 'degree'}, 'column': {'magnitude': 0.03, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>[50, 40, 80, 45]</t>
+          <t>[-16, 46, 13, 62.74324035644531]</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', None]</t>
+          <t>['2020-01-01T00:00:00.000Z', '2020-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Temperature']</t>
         </is>
       </c>
       <c r="N229" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O229" t="n">
         <v>2</v>
       </c>
       <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>2020-12-31</t>
+        </is>
+      </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_ATLANTIC_gulf_stream_destabilization_point-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/NORTHWESTSHELF_OMI_TEMPSAL_extreme_var_temp_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -17770,30 +17776,34 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Black Sea Rim Current Intensity Index</t>
+          <t>Gulf Stream destabilization point</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_BLKSEA_rim_current_index.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_ATLANTIC_gulf_stream_destabilization_point.png</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr"/>
+          <t>['Satellite observations']</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>['Black Sea']</t>
+          <t>['Global Ocean']</t>
         </is>
       </c>
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -17803,12 +17813,12 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>[31.5, 41.5, 39, 45]</t>
+          <t>[50, 40, 80, 45]</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>['1992-01-01T00:00:00.000Z', None]</t>
+          <t>['1993-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -17820,13 +17830,13 @@
         <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P230" t="inlineStr"/>
       <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_BLKSEA_rim_current_index-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_ATLANTIC_gulf_stream_destabilization_point-hq.png</t>
         </is>
       </c>
     </row>
@@ -17838,63 +17848,63 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Kuroshio Phase from Observations Reprocessing</t>
+          <t>Black Sea Rim Current Intensity Index</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_PACIFIC_kuroshio_phase_area_averaged.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_BLKSEA_rim_current_index.png</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>['Global Ocean']</t>
+          <t>['Black Sea']</t>
         </is>
       </c>
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
-          <t>1993-01-15</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>[-180, -90, 180, 90]</t>
+          <t>[31.5, 41.5, 39, 45]</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>['1993-01-15T00:00:00.000Z', None]</t>
+          <t>['1992-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>['Velocity']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="N231" t="b">
         <v>0</v>
       </c>
       <c r="O231" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P231" t="inlineStr"/>
       <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_PACIFIC_kuroshio_phase_area_averaged-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_BLKSEA_rim_current_index-hq.png</t>
         </is>
       </c>
     </row>
@@ -17906,46 +17916,50 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Black Sea Overturning Circulation Index from Reanalysis</t>
+          <t>Kuroshio Phase from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_MOC_BLKSEA_area_averaged_mean.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_PACIFIC_kuroshio_phase_area_averaged.png</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>['Black Sea']</t>
+          <t>['Global Ocean']</t>
         </is>
       </c>
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1993-01-15</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr"/>
+          <t>['Monthly']</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>[-180, -90, 180, 90]</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', None]</t>
+          <t>['1993-01-15T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Velocity']</t>
         </is>
       </c>
       <c r="N232" t="b">
@@ -17958,7 +17972,7 @@
       <c r="Q232" t="inlineStr"/>
       <c r="R232" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_MOC_BLKSEA_area_averaged_mean-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_BOUNDARY_PACIFIC_kuroshio_phase_area_averaged-hq.png</t>
         </is>
       </c>
     </row>
@@ -17970,12 +17984,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Mediterranean Meridional Overturning Circulation Index from Reanalysis</t>
+          <t>Black Sea Overturning Circulation Index from Reanalysis</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_MOC_MEDSEA_area_averaged_mean.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_MOC_BLKSEA_area_averaged_mean.png</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -17986,14 +18000,14 @@
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>['Mediterranean Sea']</t>
+          <t>['Black Sea']</t>
         </is>
       </c>
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
-          <t>1987-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -18001,14 +18015,10 @@
           <t>['Yearly']</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>[-6, 30, 36, 46]</t>
-        </is>
-      </c>
+      <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>['1987-01-01T00:00:00.000Z', None]</t>
+          <t>['1993-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -18020,13 +18030,13 @@
         <v>0</v>
       </c>
       <c r="O233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P233" t="inlineStr"/>
       <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_MOC_MEDSEA_area_averaged_mean-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_MOC_BLKSEA_area_averaged_mean-hq.png</t>
         </is>
       </c>
     </row>
@@ -18038,12 +18048,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Nordic Seas Volume Transports from Reanalysis</t>
+          <t>Mediterranean Meridional Overturning Circulation Index from Reanalysis</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_VOLTRANS_ARCTIC_averaged.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_MOC_MEDSEA_area_averaged_mean.png</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -18051,58 +18061,50 @@
           <t>['Numerical models']</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>['Arctic Ocean']</t>
+          <t>['Mediterranean Sea']</t>
         </is>
       </c>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>[-180, 60, 180, 90]</t>
+          <t>[-6, 30, 36, 46]</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2024-12-15T00:00:00.000Z']</t>
+          <t>['1987-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>['Velocity']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="N234" t="b">
         <v>0</v>
       </c>
       <c r="O234" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>2024-12-15</t>
-        </is>
-      </c>
+      <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_VOLTRANS_ARCTIC_averaged-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_MOC_MEDSEA_area_averaged_mean-hq.png</t>
         </is>
       </c>
     </row>
@@ -18114,23 +18116,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Volume Transport Anomaly in Selected Vertical Sections</t>
+          <t>Nordic Seas Volume Transports from Reanalysis</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_VOLTRANS_IBI_section_integrated_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_VOLTRANS_ARCTIC_averaged.png</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>['In-situ observations', 'Numerical models']</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
+          <t>['Numerical models']</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
+          <t>['Arctic Ocean']</t>
         </is>
       </c>
       <c r="G235" t="inlineStr"/>
@@ -18142,39 +18148,39 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>[-19, 26, 5, 56]</t>
+          <t>[-180, 60, 180, 90]</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2024-12-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Velocity']</t>
         </is>
       </c>
       <c r="N235" t="b">
         <v>0</v>
       </c>
       <c r="O235" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="P235" t="inlineStr"/>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_VOLTRANS_IBI_section_integrated_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_VOLTRANS_ARCTIC_averaged-hq.png</t>
         </is>
       </c>
     </row>
@@ -18186,23 +18192,23 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Baltic Sea Ocean Freshwater Content Anomaly (0-300m) from Reanalysis</t>
+          <t>Volume Transport Anomaly in Selected Vertical Sections</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OFC_BALTIC_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_VOLTRANS_IBI_section_integrated_anomalies.png</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['In-situ observations', 'Numerical models']</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>['Baltic Sea']</t>
+          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G236" t="inlineStr"/>
@@ -18219,7 +18225,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>[9, 53, 30, 66]</t>
+          <t>[-19, 26, 5, 56]</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -18236,7 +18242,7 @@
         <v>0</v>
       </c>
       <c r="O236" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="P236" t="inlineStr"/>
       <c r="Q236" t="inlineStr">
@@ -18246,7 +18252,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OFC_BALTIC_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CIRCULATION_VOLTRANS_IBI_section_integrated_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -18258,12 +18264,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Baltic Sea Ocean Heat Content Anomaly (0-300m) from Reanalysis</t>
+          <t>Baltic Sea Ocean Freshwater Content Anomaly (0-300m) from Reanalysis</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_BALTIC_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OFC_BALTIC_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -18318,7 +18324,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_BALTIC_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OFC_BALTIC_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -18330,63 +18336,67 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Black Sea Ocean Heat Content Anomaly (0-300m) time series and trend from Reanalysis &amp; Multi-Observations Reprocessing</t>
+          <t>Baltic Sea Ocean Heat Content Anomaly (0-300m) from Reanalysis</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_BLKSEA_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_BALTIC_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>['In-situ observations', 'Numerical models']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>['Black Sea']</t>
+          <t>['Baltic Sea']</t>
         </is>
       </c>
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>[27.32, 40.86, 41.96, 46.8]</t>
+          <t>[9, 53, 30, 66]</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>['2005-01-01T00:00:00.000Z', None]</t>
+          <t>['1993-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>['Temperature']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="N238" t="b">
         <v>0</v>
       </c>
       <c r="O238" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_BLKSEA_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_BALTIC_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -18398,23 +18408,23 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Global Ocean Heat Content (0-2000m) time series and trend from Reanalysis &amp; Multi-Observations Reprocessing</t>
+          <t>Black Sea Ocean Heat Content Anomaly (0-300m) time series and trend from Reanalysis &amp; Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_area_averaged_anomalies_0_2000.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_BLKSEA_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>['In-situ observations', 'Numerical models', 'Satellite observations']</t>
+          <t>['In-situ observations', 'Numerical models']</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>['Global Ocean']</t>
+          <t>['Black Sea']</t>
         </is>
       </c>
       <c r="G239" t="inlineStr"/>
@@ -18426,17 +18436,17 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>[-180, -60, 180, 60]</t>
+          <t>[27.32, 40.86, 41.96, 46.8]</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>['2005-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['2005-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -18448,17 +18458,13 @@
         <v>0</v>
       </c>
       <c r="O239" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P239" t="inlineStr"/>
-      <c r="Q239" t="inlineStr">
-        <is>
-          <t>2023-12-31</t>
-        </is>
-      </c>
+      <c r="Q239" t="inlineStr"/>
       <c r="R239" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_area_averaged_anomalies_0_2000-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_BLKSEA_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -18470,12 +18476,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Global Ocean Heat Content (0-300m) from Reanalysis &amp; Multi-Observations Reprocessing</t>
+          <t>Global Ocean Heat Content (0-2000m) time series and trend from Reanalysis &amp; Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_area_averaged_anomalies_0_300.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_area_averaged_anomalies_0_2000.png</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -18530,7 +18536,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_area_averaged_anomalies_0_300-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_area_averaged_anomalies_0_2000-hq.png</t>
         </is>
       </c>
     </row>
@@ -18542,12 +18548,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Global Ocean Heat Content (0-700m) from Reanalysis &amp; Multi-Observations Reprocessing</t>
+          <t>Global Ocean Heat Content (0-300m) from Reanalysis &amp; Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_area_averaged_anomalies_0_700.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_area_averaged_anomalies_0_300.png</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -18602,7 +18608,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_area_averaged_anomalies_0_700-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_area_averaged_anomalies_0_300-hq.png</t>
         </is>
       </c>
     </row>
@@ -18614,12 +18620,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Global Ocean Heat Content trend map from Reanalysis &amp; Multi-Observations Reprocessing</t>
+          <t>Global Ocean Heat Content (0-700m) from Reanalysis &amp; Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_area_averaged_anomalies_0_700.png</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -18633,11 +18639,7 @@
           <t>['Global Ocean']</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.25, 'units': 'degree'}, 'column': {'magnitude': 0.25, 'units': 'degree'}}</t>
-        </is>
-      </c>
+      <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
@@ -18651,7 +18653,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>[-180, -80, 179.75, 90]</t>
+          <t>[-180, -60, 180, 60]</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18665,10 +18667,10 @@
         </is>
       </c>
       <c r="N242" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P242" t="inlineStr"/>
       <c r="Q242" t="inlineStr">
@@ -18678,7 +18680,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_area_averaged_anomalies_0_700-hq.png</t>
         </is>
       </c>
     </row>
@@ -18690,30 +18692,34 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Iberia Biscay Ireland Ocean Heat Content Anomaly (0-2000m) time series and trend from Reanalysis &amp; Multi-Observations Reprocessing</t>
+          <t>Global Ocean Heat Content trend map from Reanalysis &amp; Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_IBI_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_trend.png</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>['In-situ observations', 'Numerical models']</t>
+          <t>['In-situ observations', 'Numerical models', 'Satellite observations']</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
-          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr"/>
+          <t>['Global Ocean']</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.25, 'units': 'degree'}, 'column': {'magnitude': 0.25, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -18723,12 +18729,12 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>[-19, 26, 5, 56]</t>
+          <t>[-180, -80, 179.75, 90]</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['2005-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -18737,7 +18743,7 @@
         </is>
       </c>
       <c r="N243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O243" t="n">
         <v>7</v>
@@ -18745,12 +18751,12 @@
       <c r="P243" t="inlineStr"/>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_IBI_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_GLOBAL_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -18762,12 +18768,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Mediterranean Ocean Heat Content Anomaly (0-700m) time series and trend from Reanalysis &amp; Multi-Observations Reprocessing</t>
+          <t>Iberia Biscay Ireland Ocean Heat Content Anomaly (0-2000m) time series and trend from Reanalysis &amp; Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_MEDSEA_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_IBI_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -18778,7 +18784,7 @@
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
-          <t>['Mediterranean Sea']</t>
+          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G244" t="inlineStr"/>
@@ -18795,30 +18801,34 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>[-6, 30, 36, 46]</t>
+          <t>[-19, 26, 5, 56]</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', None]</t>
+          <t>['1993-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Temperature']</t>
         </is>
       </c>
       <c r="N244" t="b">
         <v>0</v>
       </c>
       <c r="O244" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_MEDSEA_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_IBI_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -18830,17 +18840,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Mediterranean Ocean Salt Content (0-300m)</t>
+          <t>Mediterranean Ocean Heat Content Anomaly (0-700m) time series and trend from Reanalysis &amp; Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OSC_MEDSEA_volume_mean.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_MEDSEA_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['In-situ observations', 'Numerical models']</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -18868,12 +18878,12 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2019-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>['Salinity']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="N245" t="b">
@@ -18883,14 +18893,10 @@
         <v>8</v>
       </c>
       <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr">
-        <is>
-          <t>2019-12-31</t>
-        </is>
-      </c>
+      <c r="Q245" t="inlineStr"/>
       <c r="R245" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OSC_MEDSEA_volume_mean-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OHC_MEDSEA_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -18902,12 +18908,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Sea Ice Area/Volume Transport in the Nordic Seas from Reanalysis</t>
+          <t>Mediterranean Ocean Salt Content (0-300m)</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SI_ARCTIC_transport.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OSC_MEDSEA_volume_mean.png</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -18915,58 +18921,54 @@
           <t>['Numerical models']</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>['Arctic Ocean']</t>
+          <t>['Mediterranean Sea']</t>
         </is>
       </c>
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
-          <t>1991-01-15</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>[-20, 76, 60, 80]</t>
+          <t>[-6, 30, 36, 46]</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>['1991-01-15T00:00:00.000Z', '2024-12-15T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2019-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Salinity']</t>
         </is>
       </c>
       <c r="N246" t="b">
         <v>0</v>
       </c>
       <c r="O246" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P246" t="inlineStr"/>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2019-12-31</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SI_ARCTIC_transport-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_OSC_MEDSEA_volume_mean-hq.png</t>
         </is>
       </c>
     </row>
@@ -18978,45 +18980,49 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Baltic Sea Ice Extent from Observations Reprocessing</t>
+          <t>Sea Ice Area/Volume Transport in the Nordic Seas from Reanalysis</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_SI_extent.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SI_ARCTIC_transport.png</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr"/>
+          <t>['Numerical models']</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>['Baltic Sea']</t>
+          <t>['Arctic Ocean']</t>
         </is>
       </c>
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1991-01-15</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>['Daily']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>[9, 53, 30, 66]</t>
+          <t>[-20, 76, 60, 80]</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', None]</t>
+          <t>['1991-01-15T00:00:00.000Z', '2024-12-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -19028,13 +19034,17 @@
         <v>0</v>
       </c>
       <c r="O247" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P247" t="inlineStr"/>
-      <c r="Q247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SI_BALTIC_extent-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SI_ARCTIC_transport-hq.png</t>
         </is>
       </c>
     </row>
@@ -19046,12 +19056,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Baltic Sea Ice Volume from Observations Reprocessing</t>
+          <t>Baltic Sea Ice Extent from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_SI_volume.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_SI_extent.png</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -19102,7 +19112,7 @@
       <c r="Q248" t="inlineStr"/>
       <c r="R248" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SI_BALTIC_volume-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SI_BALTIC_extent-hq.png</t>
         </is>
       </c>
     </row>
@@ -19114,12 +19124,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Baltic Sea Mean Sea Level time series and trend from Observations Reprocessing</t>
+          <t>Baltic Sea Ice Volume from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_BALTIC_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_SI_volume.png</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -19137,40 +19147,40 @@
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
-          <t>1999-02-20</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>['Multi-yearly']</t>
+          <t>['Daily']</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>[9.7, 52, 31, 66]</t>
+          <t>[9, 53, 30, 66]</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>['1999-02-20T00:00:00.000Z', None]</t>
+          <t>['1993-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>['Sea surface height']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="N249" t="b">
         <v>0</v>
       </c>
       <c r="O249" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P249" t="inlineStr"/>
       <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_BALTIC_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SI_BALTIC_volume-hq.png</t>
         </is>
       </c>
     </row>
@@ -19182,12 +19192,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Black Sea Mean Sea Level time series and trend from Observations Reprocessing</t>
+          <t>Baltic Sea Mean Sea Level time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_BLKSEA_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_BALTIC_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -19215,7 +19225,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>[27.0625, 40.0625, 41.9375, 46.9375]</t>
+          <t>[9.7, 52, 31, 66]</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -19238,7 +19248,7 @@
       <c r="Q250" t="inlineStr"/>
       <c r="R250" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_BLKSEA_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_BALTIC_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -19250,12 +19260,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>European Seas Mean Sea Level time series and trend from Observations Reprocessing</t>
+          <t>Black Sea Mean Sea Level time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_EUROPE_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_BLKSEA_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -19283,7 +19293,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>[-20, 30, 45, 60]</t>
+          <t>[27.0625, 40.0625, 41.9375, 46.9375]</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -19306,7 +19316,7 @@
       <c r="Q251" t="inlineStr"/>
       <c r="R251" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_EUROPE_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_BLKSEA_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -19318,12 +19328,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Global Ocean Mean Sea Level time series and trend from Observations Reprocessing</t>
+          <t>European Seas Mean Sea Level time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_GLOBAL_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_EUROPE_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -19334,7 +19344,7 @@
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>['Global Ocean']</t>
+          <t>['Baltic Sea']</t>
         </is>
       </c>
       <c r="G252" t="inlineStr"/>
@@ -19351,7 +19361,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>[-180, -90, 180, 90]</t>
+          <t>[-20, 30, 45, 60]</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -19368,13 +19378,13 @@
         <v>0</v>
       </c>
       <c r="O252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P252" t="inlineStr"/>
       <c r="Q252" t="inlineStr"/>
       <c r="R252" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_GLOBAL_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_EUROPE_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -19386,12 +19396,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Global Ocean Mean Sea Level trend map from Observations Reprocessing</t>
+          <t>Global Ocean Mean Sea Level time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_GLOBAL_regional_trends.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_GLOBAL_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -19405,11 +19415,7 @@
           <t>['Global Ocean']</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.25, 'units': 'degree'}, 'column': {'magnitude': 0.25, 'units': 'degree'}}</t>
-        </is>
-      </c>
+      <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
@@ -19423,7 +19429,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>[-179.875, -89.875, 179.875, 89.875]</t>
+          <t>[-180, -90, 180, 90]</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -19437,16 +19443,16 @@
         </is>
       </c>
       <c r="N253" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P253" t="inlineStr"/>
       <c r="Q253" t="inlineStr"/>
       <c r="R253" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_GLOBAL_regional_trends-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_GLOBAL_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -19458,12 +19464,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Atlantic Iberian Biscay Mean Sea Level time series and trend from Observations Reprocessing</t>
+          <t>Global Ocean Mean Sea Level trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_IBI_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_GLOBAL_regional_trends.png</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -19474,10 +19480,14 @@
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr"/>
+          <t>['Global Ocean']</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.25, 'units': 'degree'}, 'column': {'magnitude': 0.25, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
@@ -19491,7 +19501,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>[-20, 26, 10, 48]</t>
+          <t>[-179.875, -89.875, 179.875, 89.875]</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19505,7 +19515,7 @@
         </is>
       </c>
       <c r="N254" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O254" t="n">
         <v>2</v>
@@ -19514,7 +19524,7 @@
       <c r="Q254" t="inlineStr"/>
       <c r="R254" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_IBI_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_GLOBAL_regional_trends-hq.png</t>
         </is>
       </c>
     </row>
@@ -19526,12 +19536,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Mediterranean Sea Mean Sea Level time series and trend from Observations Reprocessing</t>
+          <t>Atlantic Iberian Biscay Mean Sea Level time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_MEDSEA_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_IBI_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -19542,7 +19552,7 @@
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>['Baltic Sea']</t>
+          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G255" t="inlineStr"/>
@@ -19559,7 +19569,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>[-5.94, 30.06, 36.94, 45.94]</t>
+          <t>[-20, 26, 10, 48]</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19582,7 +19592,7 @@
       <c r="Q255" t="inlineStr"/>
       <c r="R255" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_MEDSEA_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_IBI_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -19594,12 +19604,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>North West Atlantic Shelf Mean Sea Level time series and trend from Observations Reprocessing</t>
+          <t>Mediterranean Sea Mean Sea Level time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_NORTHWESTSHELF_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_MEDSEA_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -19627,7 +19637,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>[-20, 48, 13, 62]</t>
+          <t>[-5.94, 30.06, 36.94, 45.94]</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19650,7 +19660,7 @@
       <c r="Q256" t="inlineStr"/>
       <c r="R256" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_NORTHWESTSHELF_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_MEDSEA_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -19662,12 +19672,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Baltic Sea Surface Temperature anomaly time series and trend from Observations Reprocessing</t>
+          <t>North West Atlantic Shelf Mean Sea Level time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_BAL_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_NORTHWESTSHELF_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -19685,40 +19695,40 @@
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>1999-02-20</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Multi-yearly']</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>[-12, 46, 32.01, 67.99]</t>
+          <t>[-20, 48, 13, 62]</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', None]</t>
+          <t>['1999-02-20T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>['Temperature']</t>
+          <t>['Sea surface height']</t>
         </is>
       </c>
       <c r="N257" t="b">
         <v>0</v>
       </c>
       <c r="O257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P257" t="inlineStr"/>
       <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_BAL_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SL_NORTHWESTSHELF_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -19730,12 +19740,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Baltic Sea Surface Temperature cumulative trend map from Observations Reprocessing</t>
+          <t>Baltic Sea Surface Temperature anomaly time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_BAL_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_BAL_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -19749,11 +19759,7 @@
           <t>['Baltic Sea']</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.03, 'units': 'degree'}, 'column': {'magnitude': 0.03, 'units': 'degree'}}</t>
-        </is>
-      </c>
+      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr">
         <is>
@@ -19762,12 +19768,12 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>[-10, 48, 30, 66]</t>
+          <t>[-12, 46, 32.01, 67.99]</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19781,7 +19787,7 @@
         </is>
       </c>
       <c r="N258" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
         <v>1</v>
@@ -19790,7 +19796,7 @@
       <c r="Q258" t="inlineStr"/>
       <c r="R258" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_BAL_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_BAL_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -19802,12 +19808,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Iberia Biscay Ireland Sea Surface Temperature time series and trend from Observations Reprocessing</t>
+          <t>Baltic Sea Surface Temperature cumulative trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IBI_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_BAL_trend.png</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -19818,10 +19824,14 @@
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr"/>
+          <t>['Baltic Sea']</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.03, 'units': 'degree'}, 'column': {'magnitude': 0.03, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
@@ -19830,12 +19840,12 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>[-19, 26, 5, 56]</t>
+          <t>[-10, 48, 30, 66]</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19849,16 +19859,16 @@
         </is>
       </c>
       <c r="N259" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O259" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P259" t="inlineStr"/>
       <c r="Q259" t="inlineStr"/>
       <c r="R259" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IBI_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_BAL_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -19870,12 +19880,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Iberia Biscay Ireland Sea Surface Temperature trend map from Observations Reprocessing</t>
+          <t>Iberia Biscay Ireland Sea Surface Temperature time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IBI_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IBI_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -19898,12 +19908,12 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>[-18.975000381469727, 26.024999618530273, 4.974999904632568, 55.974998474121094]</t>
+          <t>[-19, 26, 5, 56]</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19917,16 +19927,16 @@
         </is>
       </c>
       <c r="N260" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P260" t="inlineStr"/>
       <c r="Q260" t="inlineStr"/>
       <c r="R260" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IBI_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IBI_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -19938,12 +19948,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Arctic Sea and Sea Ice Surface Temperature anomaly based on reprocessed observations</t>
+          <t>Iberia Biscay Ireland Sea Surface Temperature trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IST_ARCTIC_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IBI_trend.png</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -19951,14 +19961,10 @@
           <t>['Satellite observations']</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
+      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
-          <t>['Arctic Ocean']</t>
+          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G261" t="inlineStr"/>
@@ -19970,17 +19976,17 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>[-179.97500610351562, 58, 179.97500610351562, 89.94999694824219]</t>
+          <t>[-18.975000381469727, 26.024999618530273, 4.974999904632568, 55.974998474121094]</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -19995,14 +20001,10 @@
         <v>1</v>
       </c>
       <c r="P261" t="inlineStr"/>
-      <c r="Q261" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
+      <c r="Q261" t="inlineStr"/>
       <c r="R261" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IST_ARCTIC_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IBI_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -20014,12 +20016,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Arctic Sea and Sea Ice Surface Temperature anomaly time series based on reprocessed observations</t>
+          <t>Arctic Sea and Sea Ice Surface Temperature anomaly based on reprocessed observations</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IST_ARCTIC_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IST_ARCTIC_anomaly.png</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -20046,12 +20048,12 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>[-180, 58, 180, 90]</t>
+          <t>[-179.97500610351562, 58, 179.97500610351562, 89.94999694824219]</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -20065,7 +20067,7 @@
         </is>
       </c>
       <c r="N262" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O262" t="n">
         <v>1</v>
@@ -20078,7 +20080,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IST_ARCTIC_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IST_ARCTIC_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -20090,12 +20092,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Arctic Sea and Sea Ice Surface Temperature 2D trend from climatology based on reprocessed observations</t>
+          <t>Arctic Sea and Sea Ice Surface Temperature anomaly time series based on reprocessed observations</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IST_ARCTIC_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IST_ARCTIC_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -20122,12 +20124,12 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>[-179.97500610351562, 58, 179.97500610351562, 89.94999694824219]</t>
+          <t>[-180, 58, 180, 90]</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -20141,7 +20143,7 @@
         </is>
       </c>
       <c r="N263" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>1</v>
@@ -20154,7 +20156,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IST_ARCTIC_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IST_ARCTIC_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -20166,12 +20168,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>European North West Shelf Sea Surface Temperature time series and trend from Observations Reprocessing</t>
+          <t>Arctic Sea and Sea Ice Surface Temperature 2D trend from climatology based on reprocessed observations</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_NORTHWESTSHELF_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IST_ARCTIC_trend.png</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -20179,10 +20181,14 @@
           <t>['Satellite observations']</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>['Atlantic: NW European Shelf', 'Atlantic: North']</t>
+          <t>['Arctic Ocean']</t>
         </is>
       </c>
       <c r="G264" t="inlineStr"/>
@@ -20194,17 +20200,17 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>[-18, 48, 13, 62]</t>
+          <t>[-179.97500610351562, 58, 179.97500610351562, 89.94999694824219]</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', None]</t>
+          <t>['1982-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -20213,16 +20219,20 @@
         </is>
       </c>
       <c r="N264" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O264" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P264" t="inlineStr"/>
-      <c r="Q264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_NORTHWESTSHELF_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_IST_ARCTIC_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -20234,12 +20244,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>European North West Shelf Sea Surface Temperature trend map from Observations Reprocessing</t>
+          <t>European North West Shelf Sea Surface Temperature time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_NORTHWESTSHELF_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_NORTHWESTSHELF_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -20267,7 +20277,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>[-17.975000381469727, 48.025001525878906, 12.975000381469727, 61.974998474121094]</t>
+          <t>[-18, 48, 13, 62]</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -20281,16 +20291,16 @@
         </is>
       </c>
       <c r="N265" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P265" t="inlineStr"/>
       <c r="Q265" t="inlineStr"/>
       <c r="R265" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_NORTHWESTSHELF_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_NORTHWESTSHELF_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -20302,67 +20312,63 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Baltic Sea Subsurface Salinity trend from Reanalysis</t>
+          <t>European North West Shelf Sea Surface Temperature trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_TEMPSAL_Stz_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_NORTHWESTSHELF_trend.png</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
-          <t>['Baltic Sea']</t>
+          <t>['Atlantic: NW European Shelf', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>['Multi-yearly']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>[9, 53, 30, 66]</t>
+          <t>[-17.975000381469727, 48.025001525878906, 12.975000381469727, 61.974998474121094]</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Temperature']</t>
         </is>
       </c>
       <c r="N266" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O266" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P266" t="inlineStr"/>
-      <c r="Q266" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
+      <c r="Q266" t="inlineStr"/>
       <c r="R266" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_TEMPSAL_BALTIC_Stz_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_SST_NORTHWESTSHELF_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -20374,12 +20380,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Baltic Sea Subsurface Temperature trend from Reanalysis</t>
+          <t>Baltic Sea Subsurface Salinity trend from Reanalysis</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_TEMPSAL_Ttz_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_TEMPSAL_Stz_trend.png</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -20434,7 +20440,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_TEMPSAL_BALTIC_Ttz_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_TEMPSAL_BALTIC_Stz_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -20446,12 +20452,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Iberia Biscay Ireland Sea Surface Temperature extreme from Reanalysis</t>
+          <t>Baltic Sea Subsurface Temperature trend from Reanalysis</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_TEMPSAL_IBI_extreme_var_mean_and_anomaly.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_TEMPSAL_Ttz_trend.png</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -20462,14 +20468,10 @@
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.028, 'units': 'degree'}, 'column': {'magnitude': 0.028, 'units': 'degree'}}</t>
-        </is>
-      </c>
+          <t>['Baltic Sea']</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
@@ -20478,17 +20480,17 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>['Multi-yearly']</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>[-19, 26, 4.999999046325684, 56]</t>
+          <t>[9, 53, 30, 66]</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -20497,20 +20499,20 @@
         </is>
       </c>
       <c r="N268" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O268" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P268" t="inlineStr"/>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_TEMPSAL_IBI_extreme_var_mean_and_anomaly-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_TEMPSAL_BALTIC_Ttz_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -20522,30 +20524,34 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Global Ocean Thermosteric Sea Level anomaly (0-2000m) time series and trend from Reanalysis &amp; Multi-Observations Reprocessing</t>
+          <t>Iberia Biscay Ireland Sea Surface Temperature extreme from Reanalysis</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_THSL_GLOBAL_area_averaged_anomalies_0_2000.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_TEMPSAL_IBI_extreme_var_mean_and_anomaly.png</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>['In-situ observations', 'Numerical models', 'Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>['Global Ocean']</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr"/>
+          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.028, 'units': 'degree'}, 'column': {'magnitude': 0.028, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -20555,24 +20561,24 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>[-180, -60, 180, 60]</t>
+          <t>[-19, 26, 4.999999046325684, 56]</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>['2005-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>['Sea surface height']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="N269" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O269" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P269" t="inlineStr"/>
       <c r="Q269" t="inlineStr">
@@ -20582,7 +20588,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_THSL_GLOBAL_area_averaged_anomalies_0_2000-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_TEMPSAL_IBI_extreme_var_mean_and_anomaly-hq.png</t>
         </is>
       </c>
     </row>
@@ -20594,12 +20600,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Global Ocean Thermosteric Sea Level anomaly (0-700m) time series and trend from Reanalysis &amp; Multi-Observations Reprocessing</t>
+          <t>Global Ocean Thermosteric Sea Level anomaly (0-2000m) time series and trend from Reanalysis &amp; Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_THSL_GLOBAL_area_averaged_anomalies_0_700.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_THSL_GLOBAL_area_averaged_anomalies_0_2000.png</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -20654,7 +20660,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_THSL_GLOBAL_area_averaged_anomalies_0_700-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_THSL_GLOBAL_area_averaged_anomalies_0_2000-hq.png</t>
         </is>
       </c>
     </row>
@@ -20666,12 +20672,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Global Ocean Thermosteric Sea Level trend map from Reanalysis &amp; Multi-Observations Reprocessing</t>
+          <t>Global Ocean Thermosteric Sea Level anomaly (0-700m) time series and trend from Reanalysis &amp; Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_THSL_GLOBAL_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_THSL_GLOBAL_area_averaged_anomalies_0_700.png</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -20685,11 +20691,7 @@
           <t>['Global Ocean']</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 0.25, 'units': 'degree'}, 'column': {'magnitude': 0.25, 'units': 'degree'}}</t>
-        </is>
-      </c>
+      <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
@@ -20703,7 +20705,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>[-180, -80, 179.75, 90]</t>
+          <t>[-180, -60, 180, 60]</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20713,14 +20715,14 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Sea surface height']</t>
         </is>
       </c>
       <c r="N271" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O271" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P271" t="inlineStr"/>
       <c r="Q271" t="inlineStr">
@@ -20730,7 +20732,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_THSL_GLOBAL_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_THSL_GLOBAL_area_averaged_anomalies_0_700-hq.png</t>
         </is>
       </c>
     </row>
@@ -20742,17 +20744,17 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>North Pacific Gyre Oscillation from Observations Reprocessing</t>
+          <t>Global Ocean Thermosteric Sea Level trend map from Reanalysis &amp; Multi-Observations Reprocessing</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_CLIMVAR_PACIFIC_npgo_sla_eof_mode_projection.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_THSL_GLOBAL_trend.png</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['In-situ observations', 'Numerical models', 'Satellite observations']</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -20761,44 +20763,52 @@
           <t>['Global Ocean']</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 0.25, 'units': 'degree'}, 'column': {'magnitude': 0.25, 'units': 'degree'}}</t>
+        </is>
+      </c>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr">
         <is>
-          <t>1950-01-15</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>['Monthly']</t>
+          <t>['Yearly']</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>[0, -90, 360, 90]</t>
+          <t>[-180, -80, 179.75, 90]</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>['1950-01-15T00:00:00.000Z', None]</t>
+          <t>['2005-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>['Sea surface height']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="N272" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O272" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P272" t="inlineStr"/>
-      <c r="Q272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_CLIMVAR_PACIFIC_npgo_sla_eof_mode_projection-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_CLIMATE_THSL_GLOBAL_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -20810,71 +20820,63 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Marine Heatwave Index in the Barents Sea from Reanalysis</t>
+          <t>North Pacific Gyre Oscillation from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_EXTREME_MHW_area_averaged_anomalies.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_CLIMVAR_PACIFIC_npgo_sla_eof_mode_projection.png</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
+          <t>['Satellite observations']</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
-          <t>['Arctic Ocean']</t>
+          <t>['Global Ocean']</t>
         </is>
       </c>
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1950-01-15</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>['Daily']</t>
+          <t>['Monthly']</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>[18, 68, 55, 80]</t>
+          <t>[0, -90, 360, 90]</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1950-01-15T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Sea surface height']</t>
         </is>
       </c>
       <c r="N273" t="b">
         <v>0</v>
       </c>
       <c r="O273" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P273" t="inlineStr"/>
-      <c r="Q273" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
+      <c r="Q273" t="inlineStr"/>
       <c r="R273" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_EXTREME_MHW_area_averaged_anomalies-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_CLIMVAR_PACIFIC_npgo_sla_eof_mode_projection-hq.png</t>
         </is>
       </c>
     </row>
@@ -20886,23 +20888,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Baltic Sea sea level extreme variability mean and anomaly (observations)</t>
+          <t>Marine Heatwave Index in the Barents Sea from Reanalysis</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_BALTIC_slev_mean_and_anomaly_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_EXTREME_MHW_area_averaged_anomalies.png</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>['In-situ observations']</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr"/>
+          <t>['Numerical models']</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>['Baltic Sea']</t>
+          <t>['Arctic Ocean']</t>
         </is>
       </c>
       <c r="G274" t="inlineStr"/>
@@ -20914,39 +20920,39 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
+          <t>['Daily']</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>[18, 68, 55, 80]</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>['1993-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>[0, 50, 30.5, 67]</t>
-        </is>
-      </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
-        </is>
-      </c>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>['Sea surface height']</t>
-        </is>
-      </c>
       <c r="N274" t="b">
         <v>0</v>
       </c>
       <c r="O274" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P274" t="inlineStr"/>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_BALTIC_slev_mean_and_anomaly_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/ARCTIC_OMI_EXTREME_MHW_area_averaged_anomalies-hq.png</t>
         </is>
       </c>
     </row>
@@ -20958,12 +20964,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Iberia Biscay Ireland sea level extreme variability mean and anomaly (observations)</t>
+          <t>Baltic Sea sea level extreme variability mean and anomaly (observations)</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_IBI_slev_mean_and_anomaly_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_BALTIC_slev_mean_and_anomaly_obs.png</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -20974,7 +20980,7 @@
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
-          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
+          <t>['Baltic Sea']</t>
         </is>
       </c>
       <c r="G275" t="inlineStr"/>
@@ -20991,7 +20997,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>[-23, 26, 14, 56]</t>
+          <t>[0, 50, 30.5, 67]</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -21018,7 +21024,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_IBI_slev_mean_and_anomaly_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_BALTIC_slev_mean_and_anomaly_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -21030,12 +21036,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Mediterranean Sea sea level extreme variability mean and anomaly (observations)</t>
+          <t>Iberia Biscay Ireland sea level extreme variability mean and anomaly (observations)</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_MEDSEA_slev_mean_and_anomaly_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_IBI_slev_mean_and_anomaly_obs.png</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -21046,14 +21052,14 @@
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
-          <t>['Mediterranean Sea']</t>
+          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -21063,12 +21069,12 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>[-6, 23, 35, 52]</t>
+          <t>[-23, 26, 14, 56]</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>['2000-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -21090,7 +21096,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_MEDSEA_slev_mean_and_anomaly_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_IBI_slev_mean_and_anomaly_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -21102,12 +21108,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>North West Shelf sea level extreme variability mean and anomaly (observations)</t>
+          <t>Mediterranean Sea sea level extreme variability mean and anomaly (observations)</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_NORTHWESTSHELF_slev_mean_and_anomaly_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_MEDSEA_slev_mean_and_anomaly_obs.png</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -21118,14 +21124,14 @@
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
-          <t>['Atlantic: NW European Shelf', 'Atlantic: North']</t>
+          <t>['Mediterranean Sea']</t>
         </is>
       </c>
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -21135,12 +21141,12 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>[-13, 46, 13, 62.5]</t>
+          <t>[-6, 23, 35, 52]</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['2000-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -21162,7 +21168,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_NORTHWESTSHELF_slev_mean_and_anomaly_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_MEDSEA_slev_mean_and_anomaly_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -21174,12 +21180,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Baltic Sea sea surface temperature extreme variability mean and anomaly (observations)</t>
+          <t>North West Shelf sea level extreme variability mean and anomaly (observations)</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_BALTIC_sst_mean_and_anomaly_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_NORTHWESTSHELF_slev_mean_and_anomaly_obs.png</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -21190,14 +21196,14 @@
       <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
-          <t>['Baltic Sea']</t>
+          <t>['Atlantic: NW European Shelf', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -21207,17 +21213,17 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>[0, 50, 30.5, 67]</t>
+          <t>[-13, 46, 13, 62.5]</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>['2000-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Sea surface height']</t>
         </is>
       </c>
       <c r="N278" t="b">
@@ -21234,7 +21240,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_BALTIC_sst_mean_and_anomaly_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SL_NORTHWESTSHELF_slev_mean_and_anomaly_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -21246,12 +21252,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Iberia Biscay Ireland sea surface temperature extreme variability mean and anomaly (observations)</t>
+          <t>Baltic Sea sea surface temperature extreme variability mean and anomaly (observations)</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_IBI_sst_mean_and_anomaly_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_BALTIC_sst_mean_and_anomaly_obs.png</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -21262,7 +21268,7 @@
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
-          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
+          <t>['Baltic Sea']</t>
         </is>
       </c>
       <c r="G279" t="inlineStr"/>
@@ -21279,7 +21285,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>[-23, 26, 14, 56]</t>
+          <t>[0, 50, 30.5, 67]</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -21306,7 +21312,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_IBI_sst_mean_and_anomaly_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_BALTIC_sst_mean_and_anomaly_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -21318,12 +21324,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Mediterranean Sea sea surface temperature extreme variability mean and anomaly (observations)</t>
+          <t>Iberia Biscay Ireland sea surface temperature extreme variability mean and anomaly (observations)</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_MEDSEA_sst_mean_and_anomaly_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_IBI_sst_mean_and_anomaly_obs.png</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -21334,7 +21340,7 @@
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
-          <t>['Mediterranean Sea']</t>
+          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G280" t="inlineStr"/>
@@ -21351,7 +21357,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>[-6, 23, 35, 52]</t>
+          <t>[-23, 26, 14, 56]</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -21378,7 +21384,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_MEDSEA_sst_mean_and_anomaly_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_IBI_sst_mean_and_anomaly_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -21390,12 +21396,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>North West Shelf sea surface temperature extreme variability mean and anomaly (observations)</t>
+          <t>Mediterranean Sea sea surface temperature extreme variability mean and anomaly (observations)</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_NORTHWESTSHELF_sst_mean_and_anomaly_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_MEDSEA_sst_mean_and_anomaly_obs.png</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -21406,7 +21412,7 @@
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
-          <t>['Atlantic: NW European Shelf', 'Atlantic: North']</t>
+          <t>['Mediterranean Sea']</t>
         </is>
       </c>
       <c r="G281" t="inlineStr"/>
@@ -21423,7 +21429,7 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>[-13, 46, 13, 62.5]</t>
+          <t>[-6, 23, 35, 52]</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -21450,7 +21456,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_NORTHWESTSHELF_sst_mean_and_anomaly_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_MEDSEA_sst_mean_and_anomaly_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -21462,30 +21468,30 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Global Ocean, extreme and mean significant wave height trends from satellite observations - seasonal trends</t>
+          <t>North West Shelf sea surface temperature extreme variability mean and anomaly (observations)</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_STATE_GLOBAL_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_NORTHWESTSHELF_sst_mean_and_anomaly_obs.png</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
+          <t>['In-situ observations']</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
-          <t>['Global Ocean']</t>
+          <t>['Atlantic: NW European Shelf', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
-          <t>2001-11-15</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -21495,12 +21501,12 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>[-179, -89, 179, 89]</t>
+          <t>[-13, 46, 13, 62.5]</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>['2001-11-15T00:00:00.000Z', None]</t>
+          <t>['2000-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -21509,16 +21515,20 @@
         </is>
       </c>
       <c r="N282" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O282" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="P282" t="inlineStr"/>
-      <c r="Q282" t="inlineStr"/>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_STATE_GLOBAL_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_SST_NORTHWESTSHELF_sst_mean_and_anomaly_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -21530,30 +21540,30 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Baltic Sea significant wave height extreme variability mean and anomaly (observations)</t>
+          <t>Global Ocean, extreme and mean significant wave height trends from satellite observations - seasonal trends</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_BALTIC_swh_mean_and_anomaly_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_STATE_GLOBAL_trend.png</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>['In-situ observations']</t>
+          <t>['Satellite observations']</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>['Baltic Sea']</t>
+          <t>['Global Ocean']</t>
         </is>
       </c>
       <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>2001-11-15</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -21563,34 +21573,30 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>[0, 50, 30.5, 67]</t>
+          <t>[-179, -89, 179, 89]</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>['2000-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
+          <t>['2001-11-15T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>['Wave']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="N283" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O283" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P283" t="inlineStr"/>
-      <c r="Q283" t="inlineStr">
-        <is>
-          <t>2023-12-31</t>
-        </is>
-      </c>
+      <c r="Q283" t="inlineStr"/>
       <c r="R283" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_BALTIC_swh_mean_and_anomaly_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_STATE_GLOBAL_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -21602,63 +21608,67 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Black Sea extreme wave events</t>
+          <t>Baltic Sea significant wave height extreme variability mean and anomaly (observations)</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_BLKSEA_recent_changes.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_BALTIC_swh_mean_and_anomaly_obs.png</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['In-situ observations']</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>['Black Sea']</t>
+          <t>['Baltic Sea']</t>
         </is>
       </c>
       <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
-          <t>1950-01-01</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>[27.25, 40.5, 42, 47]</t>
+          <t>[0, 50, 30.5, 67]</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>['1950-01-01T00:00:00.000Z', None]</t>
+          <t>['2000-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Wave']</t>
         </is>
       </c>
       <c r="N284" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P284" t="inlineStr"/>
-      <c r="Q284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_BLKSEA_recent_changes-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_BALTIC_swh_mean_and_anomaly_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -21670,12 +21680,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Black Sea wave power</t>
+          <t>Black Sea extreme wave events</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_BLKSEA_wave_power.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_BLKSEA_recent_changes.png</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -21726,7 +21736,7 @@
       <c r="Q285" t="inlineStr"/>
       <c r="R285" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_BLKSEA_wave_power-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_BLKSEA_recent_changes-hq.png</t>
         </is>
       </c>
     </row>
@@ -21738,67 +21748,63 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Iberia Biscay Ireland significant wave height extreme variability mean and anomaly (observations)</t>
+          <t>Black Sea wave power</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_IBI_swh_mean_and_anomaly_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_BLKSEA_wave_power.png</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>['In-situ observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
+          <t>['Black Sea']</t>
         </is>
       </c>
       <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>1950-01-01</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
+          <t>['Yearly']</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>[27.25, 40.5, 42, 47]</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>['1950-01-01T00:00:00.000Z', None]</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>[-23, 26, 14, 56]</t>
-        </is>
-      </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t>['2000-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
-        </is>
-      </c>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>['Wave']</t>
-        </is>
-      </c>
       <c r="N286" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O286" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P286" t="inlineStr"/>
-      <c r="Q286" t="inlineStr">
-        <is>
-          <t>2023-12-31</t>
-        </is>
-      </c>
+      <c r="Q286" t="inlineStr"/>
       <c r="R286" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_IBI_swh_mean_and_anomaly_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_BLKSEA_wave_power-hq.png</t>
         </is>
       </c>
     </row>
@@ -21810,12 +21816,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Mediterranean Sea significant wave height extreme variability mean and anomaly (observations)</t>
+          <t>Iberia Biscay Ireland significant wave height extreme variability mean and anomaly (observations)</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_MEDSEA_swh_mean_and_anomaly_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_IBI_swh_mean_and_anomaly_obs.png</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -21826,7 +21832,7 @@
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>['Mediterranean Sea']</t>
+          <t>['Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G287" t="inlineStr"/>
@@ -21843,7 +21849,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>[-6, 23, 35, 52]</t>
+          <t>[-23, 26, 14, 56]</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -21870,7 +21876,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_MEDSEA_swh_mean_and_anomaly_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_IBI_swh_mean_and_anomaly_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -21882,12 +21888,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>North West Shelf significant wave height extreme variability mean and anomaly (observations)</t>
+          <t>Mediterranean Sea significant wave height extreme variability mean and anomaly (observations)</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_NORTHWESTSHELF_swh_mean_and_anomaly_obs.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_MEDSEA_swh_mean_and_anomaly_obs.png</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -21898,7 +21904,7 @@
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
-          <t>['Atlantic: NW European Shelf', 'Atlantic: North']</t>
+          <t>['Mediterranean Sea']</t>
         </is>
       </c>
       <c r="G288" t="inlineStr"/>
@@ -21915,7 +21921,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>[-13, 46, 13, 62.5]</t>
+          <t>[-6, 23, 35, 52]</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21942,7 +21948,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_NORTHWESTSHELF_swh_mean_and_anomaly_obs-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_MEDSEA_swh_mean_and_anomaly_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -21954,63 +21960,67 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Mediterranean Water Mass Formation Rates from Reanalysis</t>
+          <t>North West Shelf significant wave height extreme variability mean and anomaly (observations)</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WMF_MEDSEA_area_averaged_mean.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_NORTHWESTSHELF_swh_mean_and_anomaly_obs.png</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
+          <t>['In-situ observations']</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
-          <t>['Mediterranean Sea']</t>
+          <t>['Atlantic: NW European Shelf', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
-          <t>1987-01-01</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>['Yearly']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>[-6, 30, 36, 46]</t>
+          <t>[-13, 46, 13, 62.5]</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>['1987-01-01T00:00:00.000Z', None]</t>
+          <t>['2000-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Wave']</t>
         </is>
       </c>
       <c r="N289" t="b">
         <v>0</v>
       </c>
       <c r="O289" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P289" t="inlineStr"/>
-      <c r="Q289" t="inlineStr"/>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WMF_MEDSEA_area_averaged_mean-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WAVE_NORTHWESTSHELF_swh_mean_and_anomaly_obs-hq.png</t>
         </is>
       </c>
     </row>
@@ -22022,67 +22032,63 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Baltic Sea summer bloom coverage</t>
+          <t>Mediterranean Water Mass Formation Rates from Reanalysis</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_BLOOM_BALTIC_spatiotemporal_coverage.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WMF_MEDSEA_area_averaged_mean.png</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>['Satellite observations']</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
+          <t>['Numerical models']</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
-          <t>['Baltic Sea']</t>
+          <t>['Mediterranean Sea']</t>
         </is>
       </c>
       <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
+          <t>['Yearly']</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>[-6, 30, 36, 46]</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>['1987-01-01T00:00:00.000Z', None]</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>[9.25, 53.25, 30.25, 65.85]</t>
-        </is>
-      </c>
-      <c r="L290" t="inlineStr">
-        <is>
-          <t>['1998-06-01T00:00:00.000Z', None]</t>
-        </is>
-      </c>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="N290" t="b">
         <v>0</v>
       </c>
       <c r="O290" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P290" t="inlineStr"/>
       <c r="Q290" t="inlineStr"/>
       <c r="R290" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_BLOOM_BALTIC_spatiotemporal_coverage-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_EXTREME_WMF_MEDSEA_area_averaged_mean-hq.png</t>
         </is>
       </c>
     </row>
@@ -22094,12 +22100,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Arctic Ocean Chlorophyll-a time series and trend from Observations Reprocessing</t>
+          <t>Baltic Sea summer bloom coverage</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_ARCTIC_OCEANCOLOUR_area_averaged_mean.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_BLOOM_BALTIC_spatiotemporal_coverage.png</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -22114,18 +22120,14 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>['Arctic Ocean']</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 1, 'units': 'km'}, 'column': {'magnitude': 1, 'units': 'km'}}</t>
-        </is>
-      </c>
+          <t>['Baltic Sea']</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
-          <t>1997-09-04</t>
+          <t>1998-06-01</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -22135,30 +22137,30 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>[-180, 65, 180, 90]</t>
+          <t>[9.25, 53.25, 30.25, 65.85]</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', None]</t>
+          <t>['1998-06-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>['Plankton']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="N291" t="b">
         <v>0</v>
       </c>
       <c r="O291" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P291" t="inlineStr"/>
       <c r="Q291" t="inlineStr"/>
       <c r="R291" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_ARCTIC_OCEANCOLOUR_area_averaged_mean-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_BLOOM_BALTIC_spatiotemporal_coverage-hq.png</t>
         </is>
       </c>
     </row>
@@ -22170,12 +22172,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>North Atlantic Ocean Chlorophyll-a time series and trend from Observations Reprocessing</t>
+          <t>Arctic Ocean Chlorophyll-a time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_ATLANTIC_OCEANCOLOUR_area_averaged_mean.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_ARCTIC_OCEANCOLOUR_area_averaged_mean.png</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -22190,7 +22192,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>['Baltic Sea', 'Mediterranean Sea', 'Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
+          <t>['Arctic Ocean']</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -22211,7 +22213,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>[-46, 20, 13, 66]</t>
+          <t>[-180, 65, 180, 90]</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -22234,7 +22236,7 @@
       <c r="Q292" t="inlineStr"/>
       <c r="R292" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_ATLANTIC_OCEANCOLOUR_area_averaged_mean-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_ARCTIC_OCEANCOLOUR_area_averaged_mean-hq.png</t>
         </is>
       </c>
     </row>
@@ -22246,12 +22248,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>North Atlantic Ocean Eutrophication from Observations Reprocessing</t>
+          <t>North Atlantic Ocean Chlorophyll-a time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_ATLANTIC_OCEANCOLOUR_eutrophication.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_ATLANTIC_OCEANCOLOUR_area_averaged_mean.png</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -22277,7 +22279,7 @@
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>1997-09-04</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -22287,34 +22289,30 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>[-45.99479293823242, 20.00520896911621, 12.994791984558105, 65.99478912353516]</t>
+          <t>[-46, 20, 13, 66]</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2021-12-31T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Plankton']</t>
         </is>
       </c>
       <c r="N293" t="b">
+        <v>0</v>
+      </c>
+      <c r="O293" t="n">
         <v>1</v>
       </c>
-      <c r="O293" t="n">
-        <v>2</v>
-      </c>
       <c r="P293" t="inlineStr"/>
-      <c r="Q293" t="inlineStr">
-        <is>
-          <t>2021-12-31</t>
-        </is>
-      </c>
+      <c r="Q293" t="inlineStr"/>
       <c r="R293" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_ATLANTIC_OCEANCOLOUR_eutrophication-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_ATLANTIC_OCEANCOLOUR_area_averaged_mean-hq.png</t>
         </is>
       </c>
     </row>
@@ -22326,12 +22324,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Baltic Sea Chlorophyll-a time series and trend from Observations Reprocessing</t>
+          <t>North Atlantic Ocean Eutrophication from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BALTIC_area_averaged_mean.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_ATLANTIC_OCEANCOLOUR_eutrophication.png</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -22346,7 +22344,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>['Baltic Sea']</t>
+          <t>['Baltic Sea', 'Mediterranean Sea', 'Atlantic: Iberia-Biscay-Ireland', 'Atlantic: North']</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -22357,7 +22355,7 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
-          <t>1997-09-14</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -22367,30 +22365,34 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>[9.25, 53.25, 30.25, 65.85]</t>
+          <t>[-45.99479293823242, 20.00520896911621, 12.994791984558105, 65.99478912353516]</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>['1997-09-14T00:00:00.000Z', None]</t>
+          <t>['2021-01-01T00:00:00.000Z', '2021-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>['Plankton']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="N294" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O294" t="n">
         <v>2</v>
       </c>
       <c r="P294" t="inlineStr"/>
-      <c r="Q294" t="inlineStr"/>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
+      </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BALTIC_area_averaged_mean-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_ATLANTIC_OCEANCOLOUR_eutrophication-hq.png</t>
         </is>
       </c>
     </row>
@@ -22402,12 +22404,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Baltic Sea Chlorophyll-a trend map from Observations Reprocessing</t>
+          <t>Baltic Sea Chlorophyll-a time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BALTIC_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BALTIC_area_averaged_mean.png</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -22425,11 +22427,15 @@
           <t>['Baltic Sea']</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 1, 'units': 'km'}, 'column': {'magnitude': 1, 'units': 'km'}}</t>
+        </is>
+      </c>
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
-          <t>1997-09-04</t>
+          <t>1997-09-14</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -22439,12 +22445,12 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>[9.25, 53.25, 30.24993896484375, 65.84907531738281]</t>
+          <t>[9.25, 53.25, 30.25, 65.85]</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', None]</t>
+          <t>['1997-09-14T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -22453,16 +22459,16 @@
         </is>
       </c>
       <c r="N295" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P295" t="inlineStr"/>
       <c r="Q295" t="inlineStr"/>
       <c r="R295" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BALTIC_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BALTIC_area_averaged_mean-hq.png</t>
         </is>
       </c>
     </row>
@@ -22474,12 +22480,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Black Sea Chlorophyll-a time series and trend from Observations Reprocessing</t>
+          <t>Baltic Sea Chlorophyll-a trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BLKSEA_area_averaged_mean.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BALTIC_trend.png</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -22494,18 +22500,14 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>['Black Sea']</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 1, 'units': 'km'}, 'column': {'magnitude': 1, 'units': 'km'}}</t>
-        </is>
-      </c>
+          <t>['Baltic Sea']</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1997-09-04</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -22515,12 +22517,12 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>[26.5, 40, 42, 48]</t>
+          <t>[9.25, 53.25, 30.24993896484375, 65.84907531738281]</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>['1997-01-01T00:00:00.000Z', None]</t>
+          <t>['1997-09-04T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -22529,16 +22531,16 @@
         </is>
       </c>
       <c r="N296" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O296" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P296" t="inlineStr"/>
       <c r="Q296" t="inlineStr"/>
       <c r="R296" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BLKSEA_area_averaged_mean-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BALTIC_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -22550,12 +22552,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Black Sea Chlorophyll-a trend map from Observations Reprocessing</t>
+          <t>Black Sea Chlorophyll-a time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BLKSEA_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BLKSEA_area_averaged_mean.png</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -22573,7 +22575,11 @@
           <t>['Black Sea']</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 1, 'units': 'km'}, 'column': {'magnitude': 1, 'units': 'km'}}</t>
+        </is>
+      </c>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
@@ -22587,7 +22593,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>[26.5, 40, 42.000640869140625, 48.000038146972656]</t>
+          <t>[26.5, 40, 42, 48]</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -22601,16 +22607,16 @@
         </is>
       </c>
       <c r="N297" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P297" t="inlineStr"/>
       <c r="Q297" t="inlineStr"/>
       <c r="R297" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BLKSEA_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BLKSEA_area_averaged_mean-hq.png</t>
         </is>
       </c>
     </row>
@@ -22622,12 +22628,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>North Atlantic Gyre Area Chlorophyll-a time series and trend from Observations Reprocessing</t>
+          <t>Black Sea Chlorophyll-a trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_nag_area_mean.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BLKSEA_trend.png</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -22642,14 +22648,14 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>['Global Ocean']</t>
+          <t>['Black Sea']</t>
         </is>
       </c>
       <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
-          <t>1997-09-04</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -22659,12 +22665,12 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>[-85, 5, 0, 45]</t>
+          <t>[26.5, 40, 42.000640869140625, 48.000038146972656]</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', None]</t>
+          <t>['1997-01-01T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -22673,7 +22679,7 @@
         </is>
       </c>
       <c r="N298" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O298" t="n">
         <v>1</v>
@@ -22682,7 +22688,7 @@
       <c r="Q298" t="inlineStr"/>
       <c r="R298" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_nag_area_mean-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_BLKSEA_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -22694,12 +22700,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>North Pacific Gyre Area Chlorophyll-a time series and trend from Observations Reprocessing</t>
+          <t>North Atlantic Gyre Area Chlorophyll-a time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_npg_area_mean.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_nag_area_mean.png</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -22731,7 +22737,7 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>[120, 5, 260, 45]</t>
+          <t>[-85, 5, 0, 45]</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -22754,7 +22760,7 @@
       <c r="Q299" t="inlineStr"/>
       <c r="R299" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_npg_area_mean-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_nag_area_mean-hq.png</t>
         </is>
       </c>
     </row>
@@ -22766,12 +22772,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>South Atlantic Gyre Area Chlorophyll-a time series and trend from Observations Reprocessing</t>
+          <t>North Pacific Gyre Area Chlorophyll-a time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_sag_area_mean.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_npg_area_mean.png</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -22803,7 +22809,7 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>[-65, -45, 20, 5]</t>
+          <t>[120, 5, 260, 45]</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -22826,7 +22832,7 @@
       <c r="Q300" t="inlineStr"/>
       <c r="R300" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_sag_area_mean-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_npg_area_mean-hq.png</t>
         </is>
       </c>
     </row>
@@ -22838,12 +22844,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>South Pacific Gyre Area Chlorophyll-a time series and trend from Observations Reprocessing</t>
+          <t>South Atlantic Gyre Area Chlorophyll-a time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_spg_area_mean.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_sag_area_mean.png</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -22875,7 +22881,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>[148.5, -45, 290, -5]</t>
+          <t>[-65, -45, 20, 5]</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22898,7 +22904,7 @@
       <c r="Q301" t="inlineStr"/>
       <c r="R301" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_spg_area_mean-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_sag_area_mean-hq.png</t>
         </is>
       </c>
     </row>
@@ -22910,12 +22916,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Global Ocean Chlorophyll-a trend map from Observations Reprocessing</t>
+          <t>South Pacific Gyre Area Chlorophyll-a time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_spg_area_mean.png</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -22933,11 +22939,7 @@
           <t>['Global Ocean']</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>{'row': {'magnitude': 4, 'units': 'km'}, 'column': {'magnitude': 4, 'units': 'km'}}</t>
-        </is>
-      </c>
+      <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
@@ -22951,7 +22953,7 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>[-179.9791717529297, -89.97916412353516, 179.9791717529297, 89.97916412353516]</t>
+          <t>[148.5, -45, 290, -5]</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22965,7 +22967,7 @@
         </is>
       </c>
       <c r="N302" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O302" t="n">
         <v>1</v>
@@ -22974,7 +22976,7 @@
       <c r="Q302" t="inlineStr"/>
       <c r="R302" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_oligo_spg_area_mean-hq.png</t>
         </is>
       </c>
     </row>
@@ -22986,12 +22988,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Mediterranean Sea Chlorophyll-a time series and trend from Observations Reprocessing</t>
+          <t>Global Ocean Chlorophyll-a trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_MEDSEA_area_averaged_mean.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_trend.png</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -23006,12 +23008,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>['Mediterranean Sea']</t>
+          <t>['Global Ocean']</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>{'row': {'magnitude': 1, 'units': 'km'}, 'column': {'magnitude': 1, 'units': 'km'}}</t>
+          <t>{'row': {'magnitude': 4, 'units': 'km'}, 'column': {'magnitude': 4, 'units': 'km'}}</t>
         </is>
       </c>
       <c r="H303" t="inlineStr"/>
@@ -23027,7 +23029,7 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>[-6, 30, 36.5, 46]</t>
+          <t>[-179.9791717529297, -89.97916412353516, 179.9791717529297, 89.97916412353516]</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -23041,16 +23043,16 @@
         </is>
       </c>
       <c r="N303" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O303" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P303" t="inlineStr"/>
       <c r="Q303" t="inlineStr"/>
       <c r="R303" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_MEDSEA_area_averaged_mean-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_GLOBAL_OCEANCOLOUR_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -23062,12 +23064,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Mediterranean Sea Chlorophyll-a trend map from Observations Reprocessing</t>
+          <t>Mediterranean Sea Chlorophyll-a time series and trend from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_MEDSEA_trend.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_MEDSEA_area_averaged_mean.png</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -23085,7 +23087,11 @@
           <t>['Mediterranean Sea']</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>{'row': {'magnitude': 1, 'units': 'km'}, 'column': {'magnitude': 1, 'units': 'km'}}</t>
+        </is>
+      </c>
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
@@ -23099,7 +23105,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>[-6, 30, 36.50048065185547, 45.9985466003418]</t>
+          <t>[-6, 30, 36.5, 46]</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -23113,16 +23119,16 @@
         </is>
       </c>
       <c r="N304" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P304" t="inlineStr"/>
       <c r="Q304" t="inlineStr"/>
       <c r="R304" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_MEDSEA_trend-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_MEDSEA_area_averaged_mean-hq.png</t>
         </is>
       </c>
     </row>
@@ -23134,54 +23140,58 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Baltic Sea Cod Reproductive Volume from Reanalysis</t>
+          <t>Mediterranean Sea Chlorophyll-a trend map from Observations Reprocessing</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_HEALTH_codt_volume.png.</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_MEDSEA_trend.png</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>['Numerical models']</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr"/>
+          <t>['Satellite observations']</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>['Baltic Sea']</t>
+          <t>['Mediterranean Sea']</t>
         </is>
       </c>
       <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1997-09-04</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>['Daily']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>[9, 53, 30, 66]</t>
+          <t>[-6, 30, 36.50048065185547, 45.9985466003418]</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', None]</t>
+          <t>['1997-09-04T00:00:00.000Z', None]</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Plankton']</t>
         </is>
       </c>
       <c r="N305" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O305" t="n">
         <v>1</v>
@@ -23190,7 +23200,7 @@
       <c r="Q305" t="inlineStr"/>
       <c r="R305" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_TEMPSALOXY_BALTIC_cod_volume-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_CHL_MEDSEA_trend-hq.png</t>
         </is>
       </c>
     </row>
@@ -23202,17 +23212,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Baltic Sea Major Baltic Inflow: bottom salinity from Reanalysis</t>
+          <t>Baltic Sea Cod Reproductive Volume from Reanalysis</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_WMHE_mbi_bottom_salinity_arkona_bornholm.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_HEALTH_codt_volume.png.</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>['In-situ observations', 'Numerical models', 'Satellite observations']</t>
+          <t>['Numerical models']</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -23252,13 +23262,13 @@
         <v>0</v>
       </c>
       <c r="O306" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P306" t="inlineStr"/>
       <c r="Q306" t="inlineStr"/>
       <c r="R306" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_TEMPSALOXY_BALTIC_mbi_bottom_salinity_arkona_bornholm-hq.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_TEMPSALOXY_BALTIC_cod_volume-hq.png</t>
         </is>
       </c>
     </row>
@@ -23270,12 +23280,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Baltic Sea Major Baltic Inflow: time/depth evolution S,T,O2 from Observations Reprocessing</t>
+          <t>Baltic Sea Major Baltic Inflow: bottom salinity from Reanalysis</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_WMHE_mbi_sto2tz_gotland.png</t>
+          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_WMHE_mbi_bottom_salinity_arkona_bornholm.png</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -23308,27 +23318,95 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
+          <t>['1993-01-01T00:00:00.000Z', None]</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="N307" t="b">
+        <v>0</v>
+      </c>
+      <c r="O307" t="n">
+        <v>2</v>
+      </c>
+      <c r="P307" t="inlineStr"/>
+      <c r="Q307" t="inlineStr"/>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_TEMPSALOXY_BALTIC_mbi_bottom_salinity_arkona_bornholm-hq.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>CMEMS</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Baltic Sea Major Baltic Inflow: time/depth evolution S,T,O2 from Observations Reprocessing</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>https://documentation.marine.copernicus.eu/IMG/BALTIC_OMI_WMHE_mbi_sto2tz_gotland.png</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>['In-situ observations', 'Numerical models', 'Satellite observations']</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>['Baltic Sea']</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>1993-01-01</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>['Daily']</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>[9, 53, 30, 66]</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
           <t>['1993-01-01T00:00:00.000Z', '2023-12-31T00:00:00.000Z']</t>
         </is>
       </c>
-      <c r="M307" t="inlineStr">
+      <c r="M308" t="inlineStr">
         <is>
           <t>['Temperature', 'Salinity', 'Oxygen']</t>
         </is>
       </c>
-      <c r="N307" t="b">
-        <v>0</v>
-      </c>
-      <c r="O307" t="n">
+      <c r="N308" t="b">
+        <v>0</v>
+      </c>
+      <c r="O308" t="n">
         <v>3</v>
       </c>
-      <c r="P307" t="inlineStr"/>
-      <c r="Q307" t="inlineStr">
+      <c r="P308" t="inlineStr"/>
+      <c r="Q308" t="inlineStr">
         <is>
           <t>2023-12-31</t>
         </is>
       </c>
-      <c r="R307" t="inlineStr">
+      <c r="R308" t="inlineStr">
         <is>
           <t>https://documentation.marine.copernicus.eu/IMG/OMI_HEALTH_TEMPSALOXY_BALTIC_mbi_sto2tz_gotland-hq.png</t>
         </is>

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-07-21T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-07-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-07-21T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-07-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-07-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-07-20T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-07-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-07-16T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-07-26T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-07-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-07-18T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-07-25T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-20T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-27T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>['1991-01-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
+          <t>['1991-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-07-20T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-07-27T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-07-20T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-07-27T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-07-19T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-07-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-07-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-07-21T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-07-28T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-07-20T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-07-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>['1992-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['1992-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-07-21T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-07-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-07-20T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-07-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-31T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-14T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-07-20T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-07-27T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-07-21T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-07-28T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-07-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>['1987-01-01T00:00:00.000Z', '2026-05-31T23:00:00.000Z']</t>
+          <t>['1987-01-01T00:00:00.000Z', '2026-06-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>['1999-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['1999-01-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-07-17T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-07-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2024-02-28T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-07-11T15:22:36.446Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-07-18T15:37:35.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-07-12T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-07-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-07-11T15:22:36.446Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-07-18T15:11:55.330Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-06-15T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2026-06-27T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-06-22T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2026-07-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-04-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2026-04-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-06-20T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2026-07-09T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-06-27T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2026-07-06T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-07-03T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2026-07-03T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-04T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-07-03T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-07-08T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-07-08T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-08T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-07-10T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-07-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-10T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-07-10T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-07-16T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-11T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-11T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-11T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-11T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-07-11T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-07-18T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-07-11T08:40:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-07-18T10:35:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-07-11T23:54:46.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-07-19T00:19:32.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-07-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>['1995-09-15T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
+          <t>['1995-09-15T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-07-10T23:47:47.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-07-17T23:39:33.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-07-10T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-07-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-07-11T23:16:14.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-07-18T22:50:46.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-07-10T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-07-17T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-07-22T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-07-29T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-07-11T07:24:22.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-07-18T07:35:02.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-11T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-18T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-07-11T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-07-18T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-07-11T22:27:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-07-18T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-07-11T18:38:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-07-18T19:38:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-11T23:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-18T23:13:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-11T21:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-18T21:10:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-11T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-18T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-05T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-10T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-05T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-07-13T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-07-20T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-07-28T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-08-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-07-28T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-08-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-07-27T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-26T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-04-30T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-05-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-07-27T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-08-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-07-26T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-08-02T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-07-27T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-07-25T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-08-01T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-27T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-03T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-07-27T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-03T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-07-27T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-08-03T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-07-26T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-08-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>['1980-01-01T01:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
+          <t>['1980-01-01T01:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-07-27T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-07-28T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-08-04T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-07-27T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-08-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-07-28T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-08-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-07-27T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-08-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-14T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-14T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-07-27T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-08-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-07-28T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-08-04T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-07-27T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-05-31T23:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-06-30T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2024-03-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-07-24T23:00:00.000Z']</t>
+          <t>['2024-03-03T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-02-28T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-07-18T15:37:35.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-07-25T16:12:28.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-07-19T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-07-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-07-18T15:11:55.330Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-07-25T13:09:00.303Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-07-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-06-27T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2026-07-07T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-07-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2026-07-06T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-04-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2026-04-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-07-09T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2026-07-09T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-07-06T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2026-07-10T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-07-03T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2026-07-12T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-11T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-07-10T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-06T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-07-17T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-07-22T02:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-16T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-07-16T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-07-23T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-18T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-07-18T10:35:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-07-24T21:30:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-07-19T00:19:32.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-07-25T23:40:20.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-07-02T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-07-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-07-17T23:39:33.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-07-24T23:59:59.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-07-17T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-07-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-07-18T22:50:46.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-07-25T21:55:30.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-07-17T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-07-24T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-07-29T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-07-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13269,12 +13269,12 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>[-180, -78.635744, 179.999024, 82.569]</t>
+          <t>[-180, -78.635744, 179.999999, 82.569]</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>['2002-01-15T06:29:22.000Z', '2020-12-31T23:59:14.000Z']</t>
+          <t>['1991-08-03T21:22:46.000Z', '2023-12-31T23:59:59.000Z']</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -13286,7 +13286,7 @@
         <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="P168" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-07-18T07:35:02.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-07-24T17:45:56.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-18T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-25T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="O173" t="n">
-        <v>823</v>
+        <v>838</v>
       </c>
       <c r="P173" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-07-18T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-07-25T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-07-18T22:27:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-07-25T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-07-18T19:38:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-07-25T19:35:59.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-18T23:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-25T23:12:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-18T21:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-25T21:10:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-18T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-25T23:55:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-12T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-17T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-12T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-07-20T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-07-27T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-08-04T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-08-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-08-04T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-08-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-08-03T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-08-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-08-02T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-08-03T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-08-01T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-08-08T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-03T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-10T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-03T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-10T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-08-03T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-08-10T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-08-02T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-08-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-08-04T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-08-11T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-08-03T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-08-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-08-04T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-08-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-08-03T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-08-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-21T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-03-24T23:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-04-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-21T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-04-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-08-03T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-08-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-08-04T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-08-11T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-03-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2024-07-20T01:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-03-03T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
+          <t>['2024-08-06T00:00:00.000Z', '2026-08-07T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-02-28T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-03-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-07-25T16:12:28.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-08-01T16:03:07.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-07-26T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-08-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-07-25T13:09:00.303Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-08-01T14:48:24.170Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-07-26T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-07-07T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2026-07-09T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-07-06T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2026-07-15T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-04-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2026-05-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-07-09T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2026-07-09T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>['2026-06-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['2026-07-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-07-10T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2026-07-18T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-07-12T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2026-07-21T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-18T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-07-17T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-13T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-07-22T02:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-23T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-07-23T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-25T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-07-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-07-24T21:30:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-07-31T15:00:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-07-25T23:40:20.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-08-02T00:03:04.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-07-09T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-07-24T23:59:59.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-07-31T23:56:34.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-07-24T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-07-25T21:55:30.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-08-01T22:52:45.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-07-24T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-07-31T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-07-31T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-12T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-07-24T17:45:56.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-08-01T09:07:12.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-25T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-01T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-07-25T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-01T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-07-25T22:27:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-01T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-07-25T19:35:59.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-07-31T19:35:59.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-25T23:12:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-02T00:14:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-25T21:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-01T21:13:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-25T23:55:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-01T23:21:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-07-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-19T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-24T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-29T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-19T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-07-27T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-08-03T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-08-11T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-08-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-08-11T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-08-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-08-10T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-08-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-08-03T23:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-08-08T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-08-15T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-10T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-16T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-10T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-17T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-08-10T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-08-17T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-08-09T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-08-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>['1980-01-01T01:00:00.000Z', '2026-05-01T00:00:00.000Z']</t>
+          <t>['1980-01-01T01:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-08-11T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-08-18T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-08-10T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-08-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>['1950-01-08T00:00:00.000Z', '2026-06-30T23:00:00.000Z']</t>
+          <t>['1950-01-08T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-08-11T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-08-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-08-10T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-08-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-28T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-05T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-04-21T23:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-04-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-04-28T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-08-10T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-08-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-08-11T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-08-17T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-07-20T01:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2024-07-20T01:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-08-06T00:00:00.000Z', '2026-08-07T23:00:00.000Z']</t>
+          <t>['2024-08-06T00:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-08-01T16:03:07.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-08-08T16:09:25.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-08-02T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-08-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-08-01T14:48:24.170Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-08-08T14:37:09.452Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-07-09T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2026-07-21T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-07-15T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2026-07-21T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-05-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2026-05-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>['2020-01-08T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['2020-01-08T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-07-09T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2026-07-28T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>['2020-01-02T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['2020-01-02T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-07-18T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2026-07-24T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-07-21T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2026-07-30T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>['2020-01-04T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['2020-01-04T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-25T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-07-24T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-20T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-08-07T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-07T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-08-07T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-06-26T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-07-27T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-07-31T15:00:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-08-08T08:05:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-08-02T00:03:04.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-08-08T22:47:50.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-07-31T23:56:34.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-08-07T23:48:54.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-08-07T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>['1991-08-01T00:00:00.000Z', '2026-03-31T00:00:00.000Z']</t>
+          <t>['1991-08-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>['1994-06-01T00:00:00.000Z', '2026-03-21T23:00:00.000Z']</t>
+          <t>['1994-06-01T00:00:00.000Z', '2026-04-20T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>['1994-07-01T00:00:00.000Z', '2026-03-01T00:00:00.000Z']</t>
+          <t>['1994-07-01T00:00:00.000Z', '2026-04-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-08-01T22:52:45.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-08-08T22:43:08.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-07-31T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-08-07T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-12T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-19T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>['2024-06-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['2024-06-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-08-01T09:07:12.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-08-08T07:37:55.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-01T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-08T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-01T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-08T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-01T22:27:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-08T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-07-31T19:35:59.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-08T19:38:59.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-02T00:14:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-08T23:12:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-01T21:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-08T21:10:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-01T23:21:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-08T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-07-30T00:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-08-07T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-26T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-29T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-07T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-07-26T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-08-03T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-08-10T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-08-18T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-08-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-08-18T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-08-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-08-17T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-08-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-08-15T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-08-15T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-08-22T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-16T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-23T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-17T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-24T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-08-17T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-08-24T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-08-16T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-08-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-08-18T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-08-25T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-08-17T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-08-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-08-18T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-08-25T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-08-17T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-08-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-08-17T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-08-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-08-17T23:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-08-24T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>['1987-01-01T00:00:00.000Z', '2026-06-30T23:00:00.000Z']</t>
+          <t>['1987-01-01T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-07-20T01:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2024-07-20T01:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-08-06T00:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
+          <t>['2024-08-06T00:00:00.000Z', '2026-08-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-08-08T16:09:25.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-08-15T15:04:07.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-08-09T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-08-08T14:37:09.452Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-08-15T13:01:55.079Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-07-21T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2026-07-21T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-07-21T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2026-07-27T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-05-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2026-05-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-07-28T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2026-07-28T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-07-24T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2026-08-02T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-07-30T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2026-07-30T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-08-07T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-07T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-08-07T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-09T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-09T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-09T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-09T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-07-18T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-08-15T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-08-08T08:05:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-08-14T21:30:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-08-08T22:47:50.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-08-15T23:11:34.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-07-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>['1995-09-15T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
+          <t>['1995-09-15T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-08-07T23:48:54.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-08-14T23:40:43.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>['1991-12-03T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
+          <t>['1991-12-03T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-08-07T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-08-08T22:43:08.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-08-15T23:31:12.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-08-07T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-08-14T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -12986,7 +12986,7 @@
         <v>0</v>
       </c>
       <c r="O164" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P164" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-19T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-25T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>[-180, -78.635744, 179.999999, 82.569]</t>
+          <t>[-180, -78.545469, 179.999999, 81.57083399999999]</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -13286,7 +13286,7 @@
         <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="P168" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-08-08T07:37:55.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-08-15T07:42:14.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-08T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-15T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-08T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-15T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-08T22:27:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-15T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-08T19:38:59.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-15T19:00:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-08T23:12:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-15T23:14:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-08T21:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-15T21:13:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-08T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-15T23:21:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-08-07T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-08-14T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-02T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-06-17T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-08-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-07T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-02T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-08-10T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-08-17T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-08-25T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-08-25T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-08-24T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-08-15T11:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-08-28T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-08-22T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-08-29T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-23T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-30T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>['1991-01-01T00:00:00.000Z', '2026-04-30T00:00:00.000Z']</t>
+          <t>['1991-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-24T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-31T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-08-24T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-08-31T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-08-23T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-08-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-08-25T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-09-01T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-08-24T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-08-25T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-08-24T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-05T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-19T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-05T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-08-24T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-08-24T23:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-06-30T23:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-07-20T01:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2024-07-20T01:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-08-06T00:00:00.000Z', '2026-08-21T23:00:00.000Z']</t>
+          <t>['2024-08-06T00:00:00.000Z', '2026-08-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-06-01T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>['1980-01-01T00:00:00.000Z', '2026-03-31T21:00:00.000Z']</t>
+          <t>['1980-01-01T00:00:00.000Z', '2026-04-30T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-08-15T15:04:07.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-08-22T15:04:16.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-08-15T13:01:55.079Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-08-22T13:26:25.932Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-07-21T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2026-08-02T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-07-27T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2026-08-05T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-05-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2026-05-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-07-28T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2026-07-28T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-08-02T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2026-08-11T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-07-30T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2026-08-08T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-08T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-08-07T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-03T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-08-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-08-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-16T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-08-15T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-08-22T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-08-14T21:30:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-08-21T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-08-15T23:11:34.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-08-22T17:58:04.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-07-30T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-08-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-08-14T23:40:43.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-08-21T23:32:59.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-08-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-08-15T23:31:12.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-08-22T23:00:11.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-08-14T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-08-21T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-25T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-08-31T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-08-15T07:42:14.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-08-20T06:16:52.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-15T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-22T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-15T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-22T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-15T22:27:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-22T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-15T19:00:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-22T17:40:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-15T23:14:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-22T23:13:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-15T21:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-22T21:10:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-15T23:21:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-22T23:22:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-08-14T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-08-21T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-09T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-14T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-09T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-16T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-08-17T12:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-08-24T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-09-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-09-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-09-07T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-08-28T12:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-08-31T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-08-29T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-09-05T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-30T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-07T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-31T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-08-31T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-08-30T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-09-01T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-09-08T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-09-07T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-09-01T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-09-08T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-09-07T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-09-07T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-09-08T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>['1999-01-01T00:00:00.000Z', '2026-06-30T00:00:00.000Z']</t>
+          <t>['1999-01-01T00:00:00.000Z', '2026-07-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-07-20T01:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2024-07-20T01:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-08-06T00:00:00.000Z', '2026-08-28T23:00:00.000Z']</t>
+          <t>['2024-08-06T00:00:00.000Z', '2026-09-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-08-22T15:04:16.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-08-29T16:04:44.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-08-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-08-22T13:26:25.932Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-08-29T12:40:34.482Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-08-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-08-02T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2026-08-11T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-08-05T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2026-08-10T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-05-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2026-05-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-07-28T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2026-08-16T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-08-11T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2026-08-19T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-08-08T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2026-08-17T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-15T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-08-14T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-10T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-08-21T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-08-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-21T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-08-21T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-08-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-23T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-07-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-08-22T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-08-29T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-08-21T21:00:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-08-29T08:30:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-08-22T17:58:04.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-08-30T00:36:03.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-08-06T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-08-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-08-21T23:32:59.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-08-28T23:58:32.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-08-21T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-08-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-08-22T23:00:11.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-08-29T23:25:54.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-08-21T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-08-28T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-08-20T06:16:52.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-08-23T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>[-180, -90, 179.99998474121094, 90]</t>
+          <t>[-180, -90, 179.99989318847656, 90]</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-22T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-29T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="O173" t="n">
-        <v>838</v>
+        <v>758</v>
       </c>
       <c r="P173" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-22T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-29T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-22T22:27:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-29T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-22T17:40:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-08-29T17:40:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-22T23:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-30T00:12:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-22T21:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-29T21:10:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-22T23:22:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-30T00:22:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-08-21T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-08-28T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-16T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-08-05T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-08-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-21T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-28T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-16T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-23T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-08-24T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-08-31T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-09-08T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-09-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-09-08T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-09-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-09-07T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-09-14T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-08-31T11:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-09-07T05:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-09-05T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-09-12T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-07T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-14T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-09-14T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-09-14T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-09-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-09-08T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-09-15T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-09-07T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-09-14T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-09-08T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-09-15T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-09-07T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-09-14T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-19T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-26T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-19T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-05-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-09-07T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-09-14T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-09-08T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-09-15T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-07-20T01:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['2024-07-20T01:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-08-06T00:00:00.000Z', '2026-09-04T23:00:00.000Z']</t>
+          <t>['2024-08-06T00:00:00.000Z', '2026-09-11T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-08-29T16:04:44.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-09-05T16:04:21.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-08-30T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-09-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-08-29T12:40:34.482Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-09-05T12:56:24.114Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-08-30T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-09-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-08-11T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2026-08-14T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-08-10T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2026-08-20T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-05-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2026-06-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-08-16T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2026-08-16T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>['2026-07-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
+          <t>['2026-08-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-08-19T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2026-08-20T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-08-17T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2026-08-26T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-22T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-08-21T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-17T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-08-28T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-09-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-28T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-08-28T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-09-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-30T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-30T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-30T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-07-30T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-08-29T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-09-05T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-08-29T08:30:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-09-04T15:00:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-08-30T00:36:03.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-09-05T23:56:09.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-08-13T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-08-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-08-28T23:58:32.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-09-04T23:50:12.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-08-28T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-09-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-08-29T23:25:54.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-09-05T22:47:09.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-08-28T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-09-04T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-08-31T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-09-16T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-08-23T12:00:00.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-09-05T07:46:52.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-29T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-05T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>[-180, -81.02686309814453, 179.99998474121094, 90]</t>
+          <t>[-179.99998474121094, -76.4000015258789, 179.9999542236328, 90]</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-29T23:20:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-09-05T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14266,7 +14266,7 @@
         <v>0</v>
       </c>
       <c r="O181" t="n">
-        <v>160</v>
+        <v>97</v>
       </c>
       <c r="P181" t="inlineStr">
         <is>
@@ -14321,12 +14321,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>[-180, -78.73729705810547, 179.9998779296875, 90]</t>
+          <t>[-180, -59.72752380371094, 179.9752960205078, 89.99810028076172]</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-29T22:27:00.000Z']</t>
+          <t>['1860-05-24T07:00:00.000Z', '2026-09-05T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14338,7 +14338,7 @@
         <v>0</v>
       </c>
       <c r="O182" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P182" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-08-29T17:40:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-09-05T18:30:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-30T00:12:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-05T23:59:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-29T21:10:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-05T21:13:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-08-30T00:22:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-05T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-08-28T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-09-04T19:50:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-23T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-08-19T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-08-26T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-28T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-04T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-23T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-08-30T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-08-31T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-09-07T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">

--- a/outputs/excel/copernicus_marine.xlsx
+++ b/outputs/excel/copernicus_marine.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['2020-11-01T00:00:00.000Z', '2026-09-15T00:00:00.000Z']</t>
+          <t>['2020-11-01T00:00:00.000Z', '2026-09-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['2022-11-01T03:00:00.000Z', '2026-09-15T00:00:00.000Z']</t>
+          <t>['2022-11-01T03:00:00.000Z', '2026-09-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>['2021-10-01T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
+          <t>['2021-10-01T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['2021-07-05T00:00:00.000Z', '2026-09-14T23:00:00.000Z']</t>
+          <t>['2021-07-05T00:00:00.000Z', '2026-09-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['2022-08-01T00:00:00.000Z', '2026-09-07T05:00:00.000Z']</t>
+          <t>['2022-08-01T00:00:00.000Z', '2026-09-16T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['2019-08-01T00:00:00.000Z', '2026-09-12T23:00:00.000Z']</t>
+          <t>['2019-08-01T00:00:00.000Z', '2026-09-19T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-14T23:45:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-21T23:45:00.000Z']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2024-12-31T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2025-12-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-09-14T12:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-09-21T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['2021-10-01T01:00:00.000Z', '2026-09-14T12:00:00.000Z']</t>
+          <t>['2021-10-01T01:00:00.000Z', '2026-09-21T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['2022-11-01T00:00:00.000Z', '2026-09-13T00:00:00.000Z']</t>
+          <t>['2022-11-01T00:00:00.000Z', '2026-09-20T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>['2022-12-18T00:00:00.000Z', '2026-09-15T11:00:00.000Z']</t>
+          <t>['2022-12-18T00:00:00.000Z', '2026-09-22T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-09-14T23:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-09-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>['1950-01-08T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
+          <t>['1950-01-08T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>['2022-11-22T00:00:00.000Z', '2026-09-15T00:00:00.000Z']</t>
+          <t>['2022-11-22T00:00:00.000Z', '2026-09-22T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>['2022-11-26T00:00:00.000Z', '2026-09-14T23:00:00.000Z']</t>
+          <t>['2022-11-26T00:00:00.000Z', '2026-09-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>['2022-11-23T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
+          <t>['2022-11-23T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-26T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-09T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-05-26T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-06-09T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-09-14T23:00:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-09-21T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['2021-11-30T00:00:00.000Z', '2026-09-15T11:00:00.000Z']</t>
+          <t>['2021-11-30T00:00:00.000Z', '2026-09-22T11:00:00.000Z']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['2023-10-01T00:00:00.000Z', '2026-09-14T00:00:00.000Z']</t>
+          <t>['2023-10-01T00:00:00.000Z', '2026-09-21T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>['1987-01-01T00:00:00.000Z', '2026-07-31T23:00:00.000Z']</t>
+          <t>['1987-01-01T00:00:00.000Z', '2026-08-31T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>['2024-07-20T01:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
+          <t>['2024-08-02T00:00:00.000Z', '2026-09-19T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['2024-08-06T00:00:00.000Z', '2026-09-11T23:00:00.000Z']</t>
+          <t>['2024-08-06T00:00:00.000Z', '2026-09-18T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['2024-07-29T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
+          <t>['2024-07-29T00:00:00.000Z', '2026-09-18T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['2022-05-03T00:00:00.000Z', '2026-09-05T16:04:21.000Z']</t>
+          <t>['2022-05-03T00:00:00.000Z', '2026-09-12T16:24:42.000Z']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-09-06T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-09-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['2022-03-14T01:03:00.000Z', '2026-09-05T12:56:24.114Z']</t>
+          <t>['2022-03-14T01:03:00.000Z', '2026-09-12T13:13:06.860Z']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['2022-10-04T00:00:00.000Z', '2026-09-06T00:00:00.000Z']</t>
+          <t>['2022-10-04T00:00:00.000Z', '2026-09-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['2026-08-14T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2026-08-26T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>['2023-04-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2023-04-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>['2026-08-20T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2026-08-25T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>['2026-06-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2026-06-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>['2020-01-08T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
+          <t>['2020-01-08T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>['2026-08-16T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2026-09-03T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>['2020-01-02T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
+          <t>['2020-01-02T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>['2026-08-20T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2026-08-29T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>['2025-12-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2025-12-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>['2026-08-26T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2026-09-04T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>['2020-01-04T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
+          <t>['2020-01-04T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-29T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>['1997-09-04T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['1997-09-04T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>['1997-09-16T00:00:00.000Z', '2026-08-28T00:00:00.000Z']</t>
+          <t>['1997-09-16T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>['1997-09-01T00:00:00.000Z', '2026-08-24T00:00:00.000Z']</t>
+          <t>['1997-09-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>['2026-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2026-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>['2024-01-17T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2024-01-17T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>['2020-12-20T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2020-12-20T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>['2019-03-11T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['2019-03-11T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>['2024-06-19T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['2024-06-19T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>['2022-05-01T00:00:00.000Z', '2026-09-04T23:00:00.000Z']</t>
+          <t>['2022-05-01T00:00:00.000Z', '2026-09-10T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-04T23:00:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-11T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>['2008-01-01T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['2008-01-01T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>['2019-01-01T00:00:00.000Z', '2026-09-04T23:00:00.000Z']</t>
+          <t>['2019-01-01T00:00:00.000Z', '2026-09-11T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-06T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-06T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-06T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>['1982-01-01T00:00:00.000Z', '2026-08-06T00:00:00.000Z']</t>
+          <t>['1982-01-01T00:00:00.000Z', '2026-08-13T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>['2022-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2022-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>['2023-10-18T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['2023-10-18T00:00:00.000Z', '2026-09-07T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>['2022-01-02T00:00:00.000Z', '2026-09-05T12:00:00.000Z']</t>
+          <t>['2022-01-02T00:00:00.000Z', '2026-09-12T12:00:00.000Z']</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>['2023-02-02T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
+          <t>['2023-02-02T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>['2025-11-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
+          <t>['2025-11-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-10T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>['2020-09-01T12:10:00.000Z', '2026-09-04T15:00:00.000Z']</t>
+          <t>['2020-09-01T12:10:00.000Z', '2026-09-11T15:00:00.000Z']</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>['2023-11-25T06:40:00.000Z', '2026-09-05T23:56:09.000Z']</t>
+          <t>['2023-11-25T06:40:00.000Z', '2026-09-13T00:19:38.000Z']</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>['2018-01-01T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['2018-01-01T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>['1978-10-25T12:00:00.000Z', '2026-08-20T00:00:00.000Z']</t>
+          <t>['1978-10-25T12:00:00.000Z', '2026-08-27T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>['2014-10-03T20:11:44.000Z', '2026-09-04T23:50:12.000Z']</t>
+          <t>['2014-10-03T20:11:44.000Z', '2026-09-11T23:39:44.000Z']</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>['2014-10-03T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2014-10-03T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>['2016-01-01T00:00:00.000Z', '2026-09-04T00:00:00.000Z']</t>
+          <t>['2016-01-01T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>['2024-06-13T04:00:00.000Z', '2026-09-04T23:00:00.000Z']</t>
+          <t>['2024-06-13T04:00:00.000Z', '2026-09-11T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>['2024-04-01T00:00:00.000Z', '2026-08-31T00:00:00.000Z']</t>
+          <t>['2024-04-01T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>['2024-06-27T00:00:00.000Z', '2026-09-05T00:00:00.000Z']</t>
+          <t>['2024-06-27T00:00:00.000Z', '2026-09-12T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>['2023-11-21T00:00:00.000Z', '2026-09-05T22:47:09.000Z']</t>
+          <t>['2023-11-21T00:00:00.000Z', '2026-09-12T23:02:45.000Z']</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-09-04T18:00:00.000Z']</t>
+          <t>['2021-01-01T00:00:00.000Z', '2026-09-11T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>['2021-11-01T00:00:00.000Z', '2026-09-16T21:00:00.000Z']</t>
+          <t>['2021-11-01T00:00:00.000Z', '2026-09-23T21:00:00.000Z']</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>['2024-06-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
+          <t>['2024-06-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>['1986-06-02T09:00:00.000Z', '2026-09-05T07:46:52.000Z']</t>
+          <t>['1986-06-02T09:00:00.000Z', '2026-09-12T07:27:11.000Z']</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-05T23:30:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-12T23:30:00.000Z']</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>[-179.99998474121094, -76.4000015258789, 179.9999542236328, 90]</t>
+          <t>[-180, -78.8499984741211, 179.99998474121094, 90]</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>['2021-01-01T00:00:00.000Z', '2026-09-05T23:20:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-09-12T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -14266,7 +14266,7 @@
         <v>0</v>
       </c>
       <c r="O181" t="n">
-        <v>97</v>
+        <v>166</v>
       </c>
       <c r="P181" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>['1860-05-24T07:00:00.000Z', '2026-09-05T22:27:00.000Z']</t>
+          <t>['1860-05-24T07:00:00.000Z', '2026-09-12T22:27:00.000Z']</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>['1841-03-21T00:00:00.000Z', '2026-09-05T18:30:00.000Z']</t>
+          <t>['1841-03-21T00:00:00.000Z', '2026-09-12T18:39:00.000Z']</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-05T23:59:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-12T23:14:00.000Z']</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-05T21:13:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-12T21:13:00.000Z']</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>['2020-01-01T00:00:00.000Z', '2026-09-05T23:20:00.000Z']</t>
+          <t>['2020-01-01T00:00:00.000Z', '2026-09-12T23:20:00.000Z']</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>['2023-11-01T00:00:00.000Z', '2026-09-04T19:50:00.000Z']</t>
+          <t>['2023-11-01T00:00:00.000Z', '2026-09-11T13:30:00.000Z']</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-30T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>['1993-01-06T00:00:00.000Z', '2026-08-26T00:00:00.000Z']</t>
+          <t>['1993-01-06T00:00:00.000Z', '2026-09-02T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-09-04T23:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-11T23:00:00.000Z']</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15148,7 +15148,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>['2010-01-12T00:00:00.000Z', '2026-09-03T00:00:00.000Z']</t>
+          <t>['2010-01-12T00:00:00.000Z', '2026-09-11T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>['1993-01-01T00:00:00.000Z', '2026-08-30T00:00:00.000Z']</t>
+          <t>['1993-01-01T00:00:00.000Z', '2026-09-06T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>['1985-01-01T00:00:00.000Z', '2026-07-01T00:00:00.000Z']</t>
+          <t>['1985-01-01T00:00:00.000Z', '2026-08-01T00:00:00.000Z']</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>['2025-05-21T00:00:00.000Z', '2026-09-07T18:00:00.000Z']</t>
+          <t>['2025-05-21T00:00:00.000Z', '2026-09-14T18:00:00.000Z']</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
